--- a/output/briefs_summary.xlsx
+++ b/output/briefs_summary.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기술 개요 요약" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'기술 개요 요약'!$A$1:$T$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'기술 개요 요약'!$A$1:$T$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1372,8 +1372,5326 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>9517.pdf</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>듀얼 인버터 통합 CSC(Current Source Converter) 3상 EV(Electric Vehicle) 온보드 충전 기술</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>주행 인버터·모터를 재사용해 3상 그리드 직결 고속 충전을 구현하고 충전 인프라 비용을 절감하는 통합 충전 기술 제안</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>CSC(Current Source Converter) 정류와 듀얼 인버터 DC/DC(Direct Current to Direct Current), CSVM(Current Space Vector Modulation), 인터리빙, CC-CV(Constant-Current Constant-Voltage)로 PF(Power Factor)&gt;0.99, 효율93%, IEC(International Electrotechnical Commission) 61000-3-12 충족과 모터 토크 무발생 달성</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>주행 구동부 재사용으로 3상 계통 직결 충전과 혼합 에너지 저장 장치 통합을 지원하는 온보드 고속 충전 구현
+안전한 전류원 기반 정류와 토크 무발생 제어로 차량 정지 상태의 신뢰성 높은 충전 운용 확보</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>VSC(Voltage Source Converter) 통합 충전은 권선 재구성, 추가 DC/DC 단계, 충전 중 토크 발생으로 비용·손실·복잡도 증가
+기존 CSC는 SCR(Silicon Controlled Rectifier)/GTO(Gate Turn-Off Thyristor) 기반 저스위칭 주파수로 DC 링크 리플이 커 모터 누설 인덕턴스만으로 억제가 어려움</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>CSC 기반 3상 정류와 그리드 인터페이스
+  - SiC(Silicon Carbide) 쇼트키 다이오드와 MOSFET(Metal-Oxide-Semiconductor Field-Effect Transistor)/IGBT(Insulated Gate Bipolar Transistor) 조합으로 고주파 스위칭 CSC 구현
+  - LC(Inductor-Capacitor) 입력 필터 설계로 스위칭 고조파를 억제하고 IEC 61000-3-12 대응
+  - CSVM(Current Space Vector Modulation)으로 전류 지령 추종과 역률 제어
+듀얼 인버터 DC/DC와 인터리빙 저리플
+  - 오픈권선 PMSM(Permanent Magnet Synchronous Motor) 누설 인덕턴스 활용 DC 전류 링크 구성
+  - 상·인버터 간 위상 시프트 인터리빙으로 DC 링크·권선 전류 리플 저감
+  - 멀티레벨 구동으로 고전압 구동 지원과 반도체 정격 분산
+CC-CV와 밸런싱 중첩 제어 구조
+  - CC-CV(Constant-Current Constant-Voltage) 중첩 루프 설계로 두 ESU(Energy Storage Unit) 동시 충전
+  - PR(Proportional-Resonant) 그리드 전류 제어로 정현파 전류와 고역 고립
+  - 권선 전류 균형·SoC(State of Charge) 균형 제어로 토크 무발생·에너지 평형
+설계 가이드·시동·보호 로직
+  - 스위칭 주파수·리플·소자 스트레스 제약 기반 파라미터 산정
+  - 스타트업 시 전류 제한·소프트 차지로 과도 응력 완화
+  - 전류원 특성 이용한 고장 검출과 안전 차단 시퀀스 적용</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>10kW 프로토타입에서 전체 효율 93% 달성
+계통 전류 역률 PF&gt;0.99 확보 및 IEC 61000-3-12 고조파 한도 충족
+모터 권선에 균형 DC 전류만 흐르게 제어해 충전 중 토크 발생 방지</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>University of Toronto</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>A 3-Phase Electric Vehicle Charger Integrated with Dual Inverter Drive</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>University of Toronto</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>A 3-Phase Electric Vehicle Charger Integrated with Dual Inverter Drive</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 1.6</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>Figure 1.1: Overview of standard EV setup for AC level 1 charging, AC level 2 charging, andDC fast charging [8].</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 4.17</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>Figure 1.5: Circuit configurations for CSC-based integrated chargers (a) with improved DC linkinductance utilization by Shi et al. [22] and (b) with the Renault Zoe’s Chameleon charger [23]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>cn202010457644ap.pdf</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>특허</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>동기톱니벨트·내치링 기반 로봇용 감속 장치</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>기어·웜 대신 동기톱니벨트(timing belt)와 안내 구조로 감속을 구현해 소음과 충격을 줄이는 로봇 구동 모듈 개발</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>내치링(internal ring gear)·가이드풀리(guide pulley)·지지롤러(support roller)로 벨트 장력과 맞물림을 제어해 미끄럼을 방지하고 정숙성·내구성을 확보</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>로봇 관절용 감속기의 백래시(backlash)·충격·소음을 낮추고 경량·저비용 전동 모듈을 구현
+추가 가공 없이 유지보수 용이한 일체형 전동 감속 유닛을 제안</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>기어·웜·RV·하모닉 등은 강성 접촉으로 마모 후 백래시와 고소음이 발생하고 가속·감속 시 충격이 큼
+정밀 기어 가공·조립 의존으로 비용과 중량이 높고 콤팩트한 설계와 정숙성 확보가 어려움</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>동기톱니벨트 기반 감속 메커니즘
+  - 로터(rotor) 입력축과 동기톱니벨트 치합으로 회전력을 선형 이동으로 변환
+  - 벨트 길이를 축 둘레보다 길게 설계해 감속비를 기하학적으로 결정
+  - 벨트 출력 구간이 회전 프레임(frame)을 구동해 동력 출력
+내치링·가이드풀리·지지롤러 경로 형성
+  - 내치링으로 벨트 경로를 한정해 미끄럼과 이탈을 억제
+  - 가이드풀리가 벨트를 눌러 맞물림 길이를 늘리고 접촉을 유지
+  - 지지롤러·부싱(bushing)이 벨트 내측을 따라 슬라이딩 지지해 마찰을 저감
+동력 전달과 장력 관리 로직
+  - 풀리와 지지부를 벨트 내부에 배치해 항상 적정 장력을 유지
+  - 풀리·부싱의 자전과 공전으로 동활차 유사 운동을 생성해 토크 증대
+  - 긴 맞물림과 일정 궤적으로 충격과 백래시를 흡수하는 유연 전달
+전동 모듈 일체형 구조
+  - 모터 로터 축을 감속기 입력축과 동축 결합해 부품 수를 축소
+  - 베어링(bearing)으로 로터 축과 회전 프레임을 지지해 동심도와 강성을 확보
+  - 내치링과 감속부를 베이스(base)에 고정해 축방향 길이를 단축</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>톱니벨트 유연 접촉과 장력 제어로 기계적 충격과 작동 소음이 크게 저감
+내치링 제한과 긴 맞물림 구간으로 슬립(slip)을 억제해 전달 정밀도와 출력 안정성이 향상
+기어군 제거와 통합 설계로 중량과 부품 수를 줄여 제작비와 유지보수 부담을 경감</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>CNIPA</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>A reducer and an electric drive power unit and quadruped robot using the same</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Ltd.</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>CN111609095A</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig.1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>도 3의 구조의 A-A 방향 단면도</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig.5</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>전기 구동 동력 단위의 정면도</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>cn202010971984ap.pdf</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>특허</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>외전형 프레임리스 모터(Outer-rotor Frameless Motor)·외부 유성감속기(Planetary Gear Reducer) 모듈 장치</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>유성감속기 수명 한계와 예측 불가 하중 문제로 고비용인 로봇 관절 구동계를 장시간 신뢰 운용하기 위한 모듈식 서보 전동기 장치 제안</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>외전형 프레임리스 모터와 외부 유성감속기, 대형 교차 롤러 베어링(Cross-Roller Bearing), 교체식 구조로 내구와 서비스성을 높이고 전체 시스템 수명과 운영비 절감</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>유지보수 용이성과 내구 수명을 확보하는 로봇 관절용 모듈식 서보 전동기 구현
+예측 불가 축·반경 하중에서도 안정 구동 가능한 감속기 구조 제공</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>모터 내장 유성감속기 구조로 감속기·베어링이 충격 하중에 취약해 수명이 수천시간 수준에 제한
+감속기 손상 시 전체 서보를 교체해야 해 부품비·다운타임이 커 상용화에 장애</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>모터·감속기 분리 모듈화 아키텍처
+  - 유성감속기를 모터 외측 독립 모듈로 설계해 손상 시 신속 교체
+  - 링기어를 모터 하우징과 결합해 구조 강성 및 동심도 확보
+  - 체결링과 출력판을 표준화해 로봇 관절 인터페이스 호환
+외전형 프레임리스 모터 통합 설계
+  - 프레임리스 모터(Frameless Motor) 외전형으로 고토크 밀도 구현
+  - 로터 내부에 스테이터 배치, 출력축을 스테이터 중심 관통 배치
+  - 14bit 자기 엔코더(Magnetic Encoder)로 위치·속도·토크 피드백 제공
+구동기 모듈 일체화 및 배선 구조
+  - 드라이버 보호 하우징과 모터 하우징이 전자회로 수납공간 형성
+  - PCB(Printed Circuit Board) 일부를 개구로 노출해 전원·제어선 접속 용이
+  - 하우징 일체 결합으로 배선 길이 단축 및 EMI 경로 최소화
+외부 유성감속기 고내구 구성
+  - 링기어 외경과 기어 치폭 확대로 접촉응력 저감 및 수명 확보
+  - 대형 교차 롤러 베어링(Cross-Roller Bearing)으로 다축 하중 지지
+  - 태양기어와 행성기어셋을 출력판에 직결해 백래시 관리</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>감속기 모듈 교체식 구조로 고장 시 현장 교환 가능, 다운타임과 유지보수비용 감소
+대형 기어와 교차 롤러 베어링 적용으로 축·반경·모멘트 하중에 대한 내구 수명 향상
+모터·감속기 동축 구조와 표준 인터페이스로 관절 통합과 재사용성 증대</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>CNIPA</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Modular servo motor device and robot including the same</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Ltd.</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>CN112072847A</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig.1</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>모듈식 서보 모터 장치의 사시도</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig.8</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>도 4의 A-A 절단면도</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>cn202011560498ap.pdf</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>특허</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>탄성 완충층 내장 과부하 보호 행성감속기 구조</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>로봇 넘어짐·충돌 등으로 발생하는 과부하로부터 행성감속기(planetary reducer) 구동계를 보호하기 위한 내충격 구조 제안</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>강성 치면부와 탄성 완충부의 동축 중첩 및 변형 통공(through-hole) 설계로 충격 에너지 흡수와 위치 자복원 구현</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>사족 로봇(quadruped robot)·로봇 관절에서 발생하는 과부하 충격의 에너지 흡수와 치면 보호 구현
+마찰 클러치(friction clutch) 없이 부품 수와 체적을 줄이는 내충격 감속기 실현</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>마찰 미끄럼식 보호는 마찰력 생성기 등 추가 부품으로 비용·체적 증가
+감속기 기어에 과부하 충격이 직접 전달되어 치형 파손과 구동 불능 위험 상존</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>강성 치면부-탄성 완충부 동축 중첩 구조
+  - 외치(external gear teeth) 또는 내치(internal gear teeth) 치면은 금속 강체로 토크 전달
+  - 치면 안쪽 또는 바깥에 일정 강도의 탄성 완충층을 동축 삽입
+  - 충격 시 치면부가 축 또는 외층 대비 미세 변위를 허용해 하중 분산
+변형 통공 기반 순응도 조절
+  - 완충층에 변형 통공(through-hole)을 배치해 항복 전 탄성 변형 범위 확대
+  - 통공의 배열·크기로 접선(tangential)·반경(radial) 방향 강성과 감쇠 특성 조정
+  - 과부하 소멸 시 탄성 복원으로 치면부의 원위치 자복원 확보
+구성 변형과 배치 옵션
+  - 행성기어형(planet gear): 외치부 안쪽에 완충층을 두고 축·베어링 내외륜 측에 배치
+  - 링기어형(ring gear): 내치층 바깥에 완충권을 두고 접선 변형으로 에너지 흡수
+  - 내측·외측에 강체 보강부를 추가해 치면 정밀도와 내구성 유지
+제조·체결 및 시스템 통합
+  - 완충부-강체부는 나사 체결·접착·카드 결합 등으로 신뢰성 고정
+  - 재료는 폴리우레탄, 실리콘, 고무, 플라스틱 등 현장 요구에 맞춰 선택
+  - 전기모터 출력축을 태양기어(sun gear)에 직결해 로봇 관절·사족 로봇에 적용</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>탄성 변형을 이용해 충격을 분산·흡수함으로써 기어·베어링 손상 위험 저감
+동축 내장식 구조로 보호 기능을 포함하면서 부품 수와 패키징 공간 축소
+완충부 모듈화로 동일 외형에서 보호 성능 튜닝 가능, 조립·정비 용이</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>CNIPA</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>An Overload-Impact-Resistant Planetary Reducer, Robot Joint and Quadruped Robot</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Ltd.</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>CN112728014A</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Fig.图1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>행성 감속기의 전체 단면도</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>Fig.图4</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>행성 감속기의 구성 폭발도</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>OEWM·3L·TAB 결합 800V EV 4-in-1 전력 통합 시스템</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>OBC·DC 부스트·구동·HV/LV(High Voltage/Low Voltage) DC/DC를 단일 하우징에 통합해 비용·부피·질량 절감을 지향하는 800V EV 전력 아키텍처 구현</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>OEWM(Open-Ended Winding Machine)과 전력 계수 보정(PFC, Power Factor Correction) 재구성, TAB(Triple Active Bridge)·전력 분리 제어·누설 인덕턴스 최적화로 고집적·격리·안전성 달성</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>800V EV에서 OBC, DC 부스트, 구동, HV/LV 변환을 하나의 파워 일체형 플랫폼으로 구현
+갈바닉 절연·이중화 유지와 1P·3P AC·400V DC 부스트 충전을 모두 지원하는 범용 구조 실현</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>기존 IOBC는 3P 충전 부재, 갈바닉 절연 미확보, APM 미통합 등으로 차량 적용 한계
+6·9상 기계 요구 등 고복잡·고비용 구조로 승용차 중심의 대량 양산 적용 부적합</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>모터 권선·3L 인버터 재구성 기반 다중 모드 운전
+  - OEWM(Open-Ended Winding Machine)로 1P·3P AC 입력을 권선에 직접 인가
+  - 3L(Three-Level) T형 인버터를 3P Vienna 정류기·1P 토템폴 PFC로 재구성해 AC 충전 수행
+  - 인버터·권선을 인터리브드 부스트로 재배치해 400V→800V DC 부스트 충전 수행
+TAB·3포트 변압기 기반 OBC·APM 전자기 통합
+  - TAB(Triple Active Bridge)로 HV-HV·HV-LV 동시 DC/DC 변환과 포트 간 갈바닉 절연 확보
+  - 3포트 변압기에 누설 인덕턴스 내재화로 외부 인덕터·2포트 변압기 기능 통합
+  - DC 부스트·구동 시 포트1 차단해 DAB(Dual Active Bridge)로 단순화 운전
+전력 분리 제어와 GHA 모델링 기반 설계
+  - 포트 간 순환전력 0을 만족시키는 전력 분리 제어로 독립적 전력 흐름 달성
+  - GHA(Generalized Harmonic Approximation)로 PPS(Penta Phase Shift) 운전 파형 정밀 모델링
+  - FHA(Fundamental Harmonic Approximation) 대비 포트3 전류 예측 정확도 향상
+누설 인덕턴스 최적화와 이중 뱅크 APM 구조
+  - 3포트·2포트 전역 운전점에서 RMS(Root Mean Square) 전류 최소화 다목적 최적화 수행
+  - 최적 조합 L1 12μH, L2 24μH, L3 160nH로 넓은 운전 범위에서 손실 저감 확보
+  - APM(Auxiliary Power Module) 이중 뱅크 병렬로 3.6kW×2 구성과 기능 안전성 강화</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>전기 부품 VA(Volt-Ampere) 등가 기준 총 17.74 pu → 15.25 pu로 14.1% 축소, 체적·비용 저감 근거 확보
+Vienna PFC 스테이지 스위치 12개·인덕터 3개 제거, APM 1차 H브리지 스위치 8개·변압기 통합
+3포트 변압기 시제품 부피 0.286 L·질량 924.8 g로 고집적 구현과 하우징·냉각 공유 용이</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>SAE International</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>A Multifunctional Integrated Three-Level Inverter and On-Board Charger for Electric Vehicle Application</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Schaeffler</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>10.4271/2025-01-8567</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>제안된 4-in-1 통합 파워트레인 도식</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 13</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>2포트·3포트 결합 운전의 총 유효 RMS 전류 결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>WBG 기반 CSI·SIPM 결합 EV 고집적 통합 구동 시스템</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>광대역갭(WBG, Wide Bandgap) 소자 기반 전류원 인버터(CSI, Current-Source Inverter) 일체형 모터 드라이브(IMD, Integrated Motor Drive)로 EV 견인용 고전력밀도 달성</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>세라믹 AC 필터·고주파 DC 링크·SVPWM 제어·양방향 DC/DC로 물리 통합과 노이즈 억제를 달성하며 전력전자 115 kW/L, 기계 55.6 kW/L 구현</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>표면 매입형 영구자석(SIPM, Surface Inset Permanent Magnet) 기계와 CSI를 결합해 55 kW 연속·100 kW 피크 견인 구동을 소형 경량으로 구현
+공유 수랭과 강제 송풍 복합 냉각으로 전력전자와 기계의 열 한계를 안전하게 유지</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>전압원 인버터(VSI, Voltage-Source Inverter)에서 WBG 적용 시 높은 dv/dt로 EMI·단자 과전압·베어링 전류 유발
+분리 하우징·축방향 탑재·이중 냉각 구조로 IMD 체적·질량 증가와 대전력 확장성 저하</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>SiC 기반 CSI 전력단·세라믹 AC 필터 설계
+  - SiC 모듈과 직류차단 다이오드로 RVB 스위치 구성
+  - 전류 천이 루프 최소화를 위한 전력 모듈 분할 배치와 짧은 버스바 레이아웃
+  - 세라믹 커패시터 병렬로 고리플 전류 대응, 보드 높이 80 mm에서 25 mm로 축소
+고주파 DC 링크 인덕터 소형화
+  - 스위칭 80 kHz로 요구 인덕턴스 저감, 권선 수와 코어 단면 축소
+  - 토로이드 코어·리츠선·알루미늄 냉각컵 적용으로 총 체적 0.2 L 달성
+  - 양극 버스에 인덕턴스 분할 배치로 전도 공통모드 노이즈 억제
+CSI 전류 합성·이중루프 제어와 DC/DC 재생
+  - 공간벡터 PWM(SVPWM, Space Vector PWM)로 6 유효벡터와 영벡터 조합
+  - 내부 전압 P 제어와 외부 전류 PI 제어로 지령 추종과 안정도 확보
+  - 양방향 H브리지 DC/DC로 DC 링크 전류 제어와 회생 충전 수행
+공유 수랭 재킷·강제 송풍 복합 냉각
+  - 육각 외면·원형 내경 일체 하우징에 나선 유로 수랭 채널 형성
+  - 2~8.5 L/min 유량 범위 설계로 열저항 감소와 온도 균일화
+  - 로터 덕트와 공극 송풍으로 자석 6667 r/min 52.4°C, 20000 r/min 72.8°C 유지</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>전력전자 115 kW/L, 기계 55.6 kW/L의 활성 전력밀도 달성으로 제한 공간 차량 패키징 효율 향상
+세라믹 AC 필터 적용으로 전력 보드 높이 70% 축소(80 mm→25 mm), 루프 인덕턴스와 스위칭 링잉 저감
+실험 전류 THD 1.35~2.53% 달성, 준정현 전류로 권선 손실·CM EMI와 베어링 전류 위험 저감</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Transportation Electrification</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Power-Dense Integrated Motor Drive Using a WBG-Enabled Current-Source Inverter for EV Traction Applications</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>University of Wisconsin–Madison</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TTE.2025.3617908</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 3</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>방사형 장착 CSI 기반 IMD의 3차원 렌더링 도면</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 21</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>CSI 출력 전압·전류 파형의 FFT 분석</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>도시형 전기버스용 4구동 CE2I·EMR 최적 관리 시스템</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>도시형 전기버스에서 주행·제동 전 구간의 구동 에너지 소비를 최소화하기 위한 다중구동 토폴로지와 제어 체계 제안</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>에너지 거시 표현(EMR, Energetic Macroscopic Representation)과 스마트 통합 구동(CE2I, Convertisseur d’Énergie Intégré Intelligent) 기반 전역 최적 분배로 최대 32% 에너지 절감</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>단일 구동 전기버스 대비 제동 에너지 회수와 구동 효율을 동시에 극대화하는 4구동 도시버스 구동계 구현
+안전 요구를 만족하며 실도로 주행 사이클에서 즉시 적용 가능한 에너지 관리 기법 확립</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>단일 구동은 한 축만 회생 가능해 제동 에너지 다수가 마찰제동으로 손실되고 저부하 구간 효율 최적화가 제한됨
+기존 다중구동은 기계식 결합 복잡도와 질량 증가가 크고 축간 파워 분배·제동 전략의 체계적 최적화가 부재함</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>전후 축 직렬 이중 CE2I 구성의 복합 4구동 토폴로지
+  - 각 축에 두 개의 CE2I를 공통 축으로 직렬 결합
+  - 모든 CE2I 인버터를 공통 DC 버스에 병렬 접속해 전력 포트 통합
+  - 전축에 감속기·디퍼렌셜을 추가하고 단일 구동과 동일한 속도·토크 한계 유지
+EMR 기반 모델링과 역구조 제어 조직
+  - EMR으로 배터리·구동·차체 상호작용을 계층 블록으로 구성
+  - 휠력 분배, 전후 축 제동 기준, 각 CE2I 토크 지령 등 5개 제어변수 정의
+  - EMR 역구조 규칙으로 추종 제어기와 제동 우선순위 로직을 유도
+전역 탐색 기반 최적 에너지 관리
+  - 전체 트랙션 효율을 제어변수 함수로 정의하고 룩업 효율맵으로 평가
+  - 토크·속도 한계를 제약으로 힘 50 N, 토크 1 N·m 격자 전역 탐색 수행
+  - 속도 5 km/h 초과는 전기제동, 5 km/h 이하는 기계제동으로 안전 확보
+성능 검증과 공정 비교 프레임워크
+  - MATLAB/Simulink EMR 모델을 GT‑SUITE와 비교해 에너지 오차 2% 미만 검증
+  - New York, London, Denver 버스 사이클로 단일 구동과 동등 조건 비교
+  - 질량 증가 민감도와 구동기 고장 시 추종·소비 변화를 평가해 신뢰성 확인</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>실도 버스 사이클에서 에너지 소비 최대 32% 감소
+트랙션 평균 효율 최대 6.5% 향상, 회생 배터리‑휠 효율 최대 92%(단일 54%) 달성
+균등 분배만 적용해도 SORT 2에서 주행거리 4.3% 증가</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Transportation Electrification</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Energy Savings of a Four-Drive Electric Bus With Two Cascaded Smart Integrated Drives on Each Axle</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>University of Lille</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TTE.2024.3454443</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 5</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>두 구동 차축을 갖는 4구동 전기버스 구성</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 14</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>견인 모드에서 파워트레인의 평균 효율</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>인터리브드 PWM·평균보정 기반 IPMSM 부스트 충전 방법</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>400V 충전기로 800V 배터리 충전을 위해 내부 영구자석 동기전동기(IPMSM, Internal Permanent Magnet Synchronous Machine)와 인버터를 부스트 컨버터로 활용하는 온보드 충전 제어</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>전 인덕턴스 모델과 인터리브드 펄스폭 변조(PWM, Pulse Width Modulation), 이중 샘플 평균보정으로 상 평균전류 동등화와 리플 각도 의존 최소화를 구현</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>IPMSM 기반 온보드 부스트 충전에서 로터 각도 의존 리플과 상간 평균전류 불균형을 해석하고 제어
+추가 인덕터 없이 기존 구동 모터·인버터만으로 안전한 무토크 충전 운전을 실현</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>로터 saliency와 상간 결합으로 상전류 파형과 평균값이 상이해 축방향 토크가 발생
+동일 듀티 동기 PWM은 리플이 커지고, 이중 샘플 평균은 다중 꼭짓점 파형에서 오차 발생</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>고주파 영역 IPMSM 전 인덕턴스 모델링
+  - 고주파(10~20 kHz)에서 자화·누설 인덕턴스 재정의
+  - 회전자 saliency를 포함한 상간 결합 인덕턴스 모델 적용
+  - 모터 고정 회전각 조건에서 상전류 미분과 전압 관계 해석
+인터리브드 PWM 기반 승압 동작 해석
+  - 동일 듀티·120° 위상천이 인터리브드 PWM 구성
+  - 듀티에 따른 3개 모드로 스위칭 상태·전압 구간 분해
+  - 평형 상태에서 승압 전압비가 각도와 무관함을 증명
+리플·평균전류 해석과 최적 회전각 탐색
+  - 상별 리플 피크-피크와 리플 평균을 각도·듀티로 표현
+  - 스위치 전류 한계에서 허용 평균전류·충전전력 산정
+  - 테이블 기반 최적 회전각 도출(D=0.5에서 30° 등)
+이중 샘플 평균보정과 상전류 동등화 제어
+  - 상단·저점 이중 샘플의 면적 오차를 보상하는 Qa,Qb,Qc
+  - 세 상 PI 전류 루프와 보상기를 결합한 평균전류 피드백
+  - 부스트 전압비 기반 듀티 선행제어로 응답성과 안정성 확보</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>D=0.5에서 pθ=30°일 때 평균전류 149 A로 pθ=0° 136 A 대비 전력 11% 증가
+실험에서 pθ=30°에서 피크-피크 리플 11% 감소, 평균 충전전류 약 17% 증가
+Qx 적용 시 토크 0.5 Nm에서 0 Nm로 제거되어 무토크 충전 확보</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Phase Current Equalization Method of IPMSM-Based on-Board Boost Converter for Electric Vehicles</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Pohang University of Science</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/ACCESS.2023.3272382</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 3</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>통합 부스트 충전기 구성</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 17</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>Imax_sw=25A, pθ=0°·30° 입력·상전류</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5변수 룩업 기반 CF-TAB OBC·APM 통합 제어 방법</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>전기차 OBC(On-Board Charger)와 APM(Auxiliary Power Module) 통합을 위해 CF-TAB(Current-Fed Triple Active Bridge)에서 스위칭 손실 저감과 소프트스위칭(ZVS, Zero-Voltage Switching) 범위 확대를 목표로 한 제어 기술 개발</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>일반화 고조파 근사(GHA, Generalized Harmonic Approximation)와 Δ 등가 전력 모델 기반 전류·전력 해석으로 5변수 룩업 제어를 설계해 손실 저감과 ZVS 영역 확장 달성</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>OBC와 APM을 단일 CF-TAB 토폴로지로 통합해 비용·부피를 낮추고 전력 밀도를 높이는 실용 제어 구현
+광범위 전압·부하 조건에서 스위칭 손실을 최소화하고 ZVS 달성 영역을 넓히는 운전점 최적화</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>기존 TAB 최적화는 도통 손실 위주 또는 일부 스위치의 ZVS만 고려해 경부하 스위칭 손실 지배 구간 대응이 미흡함
+세 포트 CF-TAB 통합에서 출력 전류 리플과 권선비 증가, DPS(Dual Phase-Shift) 고정 제어로 ZVS 범위가 제한됨</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>CF-TAB 토폴로지 및 전력 흐름 모델링
+  - 3풀브리지·3권선 변압기 Δ 등가 모델로 포트 간 전달전력을 폐루프 제약식으로 표현
+  - HV·LV 보조단은 인터리브 병렬 Buck로 구성해 출력 전류 리플 저감
+  - GHA로 각 권선 전류를 기저파 기반 파형으로 근사해 스위칭 전류 산정
+ZVS 조건 단순화와 스위칭 손실 지표 정의
+  - 스위치 턴온 시 전류 부호로 ZVS 여부를 판정하고 기생 커패시터 에너지는 무시
+  - 하드 턴온 스위치 전류만 합산한 손실 지표 F를 최소화 대상으로 설정
+  - 초기화 시 각 스위치의 포트전류와 출력 인덕터 전류 합성으로 턴온 전류 추정
+다제약 하 5변수 운전점 최적화 프레임워크
+  - 제어변수 Dp, DH, DL, phi12, phi13 중 2개로 포트 전력 제약을 만족
+  - 잔여 3개 변수를 탐색해 스위칭 손실 지표 F를 최소화
+  - 전압·부하 전역에서 운전점별 최적 변수 조합을 산출
+실시간 구현을 위한 4차원 룩업테이블 제어
+  - 입력 축을 VoH, VoL, P2ref, P3ref로 하는 4차원 테이블 5개를 오프라인 생성
+  - 테이블은 각 축 운전점에서의 최적 Dp, DH, DL, phi12, phi13을 저장
+  - 실시간 제어기는 측정값을 키로 최적 변수를 읽어 즉시 적용</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>전역 운전점에서 DPS 대비 스위칭 손실 지표 F가 일관되게 낮아져 경부하 우세 손실을 효과적으로 억제
+변압기 3포트 피크 전류가 각각 10.35%, 30.76%, 20.6% 감소하여 스위칭 및 도통 손실 저감에 기여
+LV 보조단 인터리브로 출력 전류 리플 2A, 리플율 약 2.86%로 억제</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>IEEE ICoPESA</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Switching Loss Optimization and Soft Switching Range Extension of a Current-fed Triple Active Bridge Converter</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Nanjing University of Aeronautics</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/ICoPESA65876.2025.11234380</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 1</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>광범위 전압·부하의 DPS·제안 제어 ZVS 영역 비교</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 6</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>VoL=12V, P3=100W에서 DPS·제안 제어 ZVS 영역 비교</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3.6 kW EV APM용 인터리브드 동기벅 최적 설계 기술</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>전기차 보조전원모듈(APM, Auxiliary Power Module) 2단 구조의 인터리브드 동기벅(SBC, Synchronous Buck Converter)에서 손실과 체적을 동시 최소화하는 설계 최적화 달성</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>스위칭 주파수·위상 수·병렬 인덕터·전류 리플·결합 여부 전수 탐색과 소자·커패시터·인덕터 손실 모델을 결합해 파레토 후보를 도출하고 실험 대비 오차 RMSE 0.24% 입증</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>48 V 입력, 9~16 V 3.6 kW, 250 A 조건에서 APM 2단 SBC의 효율·전장 집적도 목표 동시 달성
+파라미터 전역 탐색으로 위상 수·주파수·인덕터 구조의 최적 조합 규명</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>기존 연구는 위상 수·주파수·리플 등 일부 변수를 고정하거나 결합·병렬 인덕터 효과를 배제
+고전류 LV 환경에서는 DCM 가정과 부분 손실 모델로 실제 손실·체적 트레이드오프 반영 한계</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>전역 설계 최적화 프레임워크
+  - MATLAB 기반 파라미터 전수 탐색으로 2060개 설계 데이터베이스 구축
+  - 스위칭 주파수, 위상 수, 병렬 인덕터 수, 전류 리플, 결합 여부를 독립 변수로 설정
+  - 각 설계에 손실, 인덕터 설계, 수동소자 체적, 높이 제약을 동시에 평가
+소자 및 커패시터 손실 모델링
+  - 데이터시트 곡선과 DPT(Double Pulse Test)로 도출한 에너지로 스위칭·도통 손실 계산
+  - 저측 스위치는 ZVS(Zero-Voltage Switching) 가정으로 스위칭 손실 무시하고 Coss 영향은 소수로 취급
+  - MLCC(Multilayer Ceramic Capacitor) ESR 주파수 LUT를 적용해 RMS(root mean square) 전류 기준 손실 산정
+인덕터 설계와 권선 손실 해석
+  - Kg 방법을 적용하고 29개 E·평면 코어와 3개 재료 라이브러리에서 후보 생성
+  - 코어 포화, 창 이용률 범위, 목표 인덕턴스를 만족하도록 권선 수와 에어갭 산정
+  - Dowell 모델로 AC·DC 권선 손실을 분리 계산하고 솔리드·리츠·포일 권선 옵션을 비교
+파레토 해석과 시제품 선정
+  - 손실 대 체적 파레토 프론트를 도출해 세 가지 대표 설계 후보를 식별
+  - 높이, 표면적, 손실의 시스템 수준 제약을 반영해 최종 후보를 결정
+  - 선정 설계에 대해 하드웨어 시제품 제작과 효율 측정으로 모델을 검증</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>모델 대 실험 효율 오차 RMSE 0.24%, 최대 오차 약 0.45%로 손실 모델 신뢰성 확보
+피크 효율 95.9%, 평균 효율 94.8%를 달성하며 9~16 V 전 영역 250 A 운전 조건 충족
+파레토 분석으로 표면적 2280 mm2의 3상 설계를 선정했고 대안 설계는 표면적이 거의 214% 커 패키징 이점 확보</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>IEEE IECON</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Optimized Interleaved Synchronous Buck Converter Design for a Two-Stage 3.6 kW Auxiliary Power Module in Electric Vehicles</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>McMaster University</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/IECON58223.2025.11221062</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 3</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>SBC 최적화 프레임워크와 인덕터 설계</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 7</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>Vin=48 V에서 Vout별 효율 측정과 모델 비교</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>가변 직렬·병렬 재구성 기반 동적 전압 전기차 배터리 시스템</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>배터리 팩을 주행 상태에 맞춰 직렬·병렬로 실시간 재구성해 효율과 성능을 동시에 달성하는 DVEVS(Dynamic Voltage EV System) 개념 정립</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>전력전자 하이브리드 스위칭과 EDLC(Electric Double-Layer Capacitor) 융합, BTMS(Battery Thermal Management System)·충전 인프라 연계를 통한 주행·충전 최적화 구현</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>고속 순항과 급가속 등 상이한 부하 조건에서 전압·전류 조건을 능동 제어해 파워트레인 효율과 성능을 동시 확보
+열·신뢰성 제약을 완화하며 다양한 충전 전압 범위를 수용하는 재구성형 전기차 배터리 아키텍처 구현</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>고정 전압 배터리 구조는 주행 조건별 최적 전압을 제공하지 못해 I2R 손실과 모터 효율 저하 발생
+충전 인프라 전압 호환 범위 제한과 열 집중으로 인한 셀 열화, 고전류 스위칭의 응답 지연과 아크 위험</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>배터리 토폴로지와 재구성 로직
+  - PCM(Parallel-Cell-Module)·SCM(Series-Cell-Module) 혼합 토폴로지로 전압·전류 범위를 유연화
+  - BMS(Battery Management System) 기반 SOC·온도·부하 추정으로 직렬·병렬 전환 시점 결정
+  - 전환 시 토크 홀·순시 전류 피크 완화를 위한 안전 시퀀스와 밸런싱 모드 적용
+전력전자 기반 하이브리드 스위칭
+  - SSR(Solid-State Relay, MOSFET·IGBT·SiC)와 컨택터 결합으로 속도와 내전류 성능 동시 확보
+  - 프리차지·스너버·디바운스 제어로 아크·인러시 억제 및 접점 스트레스 저감
+  - 센서·마이컴 통합 전력 모듈로 실시간 진단과 운전 요구 기반 적응 전환 구현
+EDLC 융합 하이브리드 에너지 관리
+  - 배터리+EDLC 병렬 운전으로 가속·회생 제동의 피크 전력 셰이빙 수행
+  - EDLC 전압 저하 시 직렬 연결로 잔여 에너지 회수하는 체인지오버 로직 적용
+  - 양방향 DC 버스와 한계 전류·전압 기반 모드 스케줄링으로 배터리 스트레스 경감
+충전 인프라 및 통신 연동
+  - LLC(Inductor–Inductor–Capacitor) 재구성 공진 컨버터와 다중 모드 정류로 200~800V 수용
+  - ISO 15118 확장 기반 EVSE(Electric Vehicle Supply Equipment)·BMS·BTMS 협조 제어
+  - 소프트 스위칭 전 구간 유지와 전압 스트레스 관리로 효율과 신뢰성 확보</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>재구성 LLC 기반 DC 충전에서 입력 400V, 출력 200~800V, 정격 500W, 피크 효율 93.9% 달성
+SSR는 마이크로초 수준, 컨택터는 10~50 ms 전환으로 부하 조건별 응답성과 내전류 성능 균형 확보
+셀 권장 온도 20~45°C 범위 유지 전략과 버스바 설계 최적화로 국부 열점 발생 위험 저감</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SAE International</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Voltage EV System (DVEVS): Achieving Enhanced Electric Vehicle Efficiency and Performance through a Switchable Series-Parallel Battery Configuration</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>10.4271/2026-26-0203</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>서로 다른 배터리 운전 모드 회로도</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 5</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>다양한 공기 유동 전략의 냉각 효율 비교</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>DAB-PSFB 기반 11 kW 통합 OBC-LDC 충전 시스템</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>EV(Electric Vehicle) 배터리의 G2V·V2G·주행 3모드를 OBC(On-Board Charger)와 LDC(Low-Voltage DC–DC Converter) 통합으로 단일 전력단에서 독립 제어하는 고전력 시스템 구현</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>DAB(Dual-Active Bridge) OBC와 PSFB(Phase-Shift Full-Bridge) LDC의 두 변압기 구조 통합, DPS(Dual Phase Shift) 제어와 OR 게이트 SR(Synchronous Rectifier) 구동, 누설 인덕턴스 최적화로 97.1% 효율 달성</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>11 kW 급에서 HV·LV 배터리를 독립 제어하며 고효율·고전력 밀도를 실현하는 OBC-LDC 통합 구조 구현
+G2V·V2G 양방향에서 동일 조건 효율 극대화를 위한 변압기·제어 변수 최적 설계</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>OBC·LDC 분리 인덕터·변압기 사용과 LDC 2차측 소자 다수로 부피·전도 손실 증가
+양방향 동작 최적화 미흡과 SR 지연 동기화로 바디 다이오드 도통 발생</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>두 변압기 통합 PSFB LDC와 DAB OBC 결합 구조
+  - LDC 출력 인덕터를 변압기 누설로 치환해 자속 경로에 통합
+  - OBC와 LDC 변압기를 병렬 자화 인덕턴스 모델로 설계해 상호 간섭 분석
+  - LDC 2차측 전도 소자와 권선을 2개로 축소해 전도 경로 단순화
+듀얼 위상천이 기반 이중 포트 독립 제어
+  - D2로 DAB 전력 이송 제어, D1로 LDC 평균 변압기 전압 제어
+  - G2V에서 D1이 D2 이상이 되도록 제약을 두어 SR 제어 복잡도 억제
+  - 주행 모드 D2=0에서 VLink 보상 메커니즘 반영해 안정 동작 확보
+OR 게이트 기반 SR 구동 로직
+  - 지연다리와 선행다리 스위치 신호를 OR 결합해 SR 게이트 생성
+  - vT 영전압 구간 전체에서 양쪽 SR 동시 도통으로 바디 다이오드 도통 차단
+  - D1,D2 관계와 VLink·VHV 변화에 무관한 vT 극성 기반 온오프 기준 적용
+누설 인덕턴스 분배와 파라미터 최적화
+  - LP와 LS를 동일화해 양방향 대칭 손실 분포와 동일 효율 조건 확보
+  - LT 한계 내에서 k를 0.5로 설정해 스위칭 전류와 rms 전류 최소화
+  - n 14, LM 1.3 μH, LT 5 μH로 LDC 전압 이득과 리플 조건 동시 충족</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>G2V·V2G 양방향에서 피크 효율 97.1% 달성, 주행 모드 최소 전압 조건에서 95% 달성
+LDC 2차측 전도 부품 수를 2개로 축소해 전도 손실 경감과 부피 저감
+VLink와 VHV가 동일한 조건에서 G2V·V2G 동일 효율 구현으로 운전 모드 간 성능 대칭 확보</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Industrial Electronics</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Design and Optimization of an 11 kW Integrated OBC-LDC EV Battery Charging System</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Inha University</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TIE.2025.3610746</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>회로도: (a) 기존 IBCS, (b) 제안 IBCS</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 18</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>측정 효율: (a) G2V/V2G 11 kW, (b) 주행 모드</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>모터·기어 통합·하이브리드 냉각·MPC 기반 e-액슬 시스템</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>모터·기어박스 통합, 열관리, 제어 알고리즘 동시 고도화로 전동 액슬 효율과 응답성 확보 목적</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2단 기어, 오일–워터 하이브리드 냉각, 도로 경사 프리뷰 모델예측제어(MPC, Model Predictive Control) 결합으로 에너지 약 10% 절감과 과도 응답 30% 가속 실현</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>신에너지차 전동 액슬의 구동 효율, 질량, 열안정성, 제어 응답을 동시 향상하는 설계·제어 프레임 구현
+하드웨어·열·소프트웨어 통합 최적화를 통해 배터리 증대 없이 주행거리 확장</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>단일 속도 기어박스의 고속 효율 저하와 다단 기어박스의 중량·부피 증가로 시스템 최적화 한계
+고부하 열집중으로 성능 열화와 제어 지연, 표준화된 극한 온도 내구 평가 부재</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>모터–기어박스 통합 설계와 경량 구조
+  - 영구자석 동기모터(PMSM, Permanent Magnet Synchronous Motor)와 2단 기어 결합으로 고속 효율 5~7% 향상
+  - 유성기어 토폴로지 최적화로 질량 15~20% 절감과 기어 메싱 소음 8~10 dB 저감
+  - 탄소섬유강화폴리머(CFRP, Carbon Fiber Reinforced Polymer) 하우징과 티타늄 매트릭스 로터로 경량·강성 확보
+액슬 공동 열관리 시스템 설계
+  - 오일–워터 하이브리드 냉각으로 모터·기어 온도 변동 ±3°C 유지와 열교환 25% 향상
+  - 상변화물질(PCM, Phase Change Material) 내장 히트싱크로 피크 온도 12~15°C 저감
+  - 그래핀 보강 열인터페이스재(TIM, Thermal Interface Material)와 나노냉매로 열전달 40~50% 및 28% 향상
+예측 제어·분산 제어 기반 소프트웨어
+  - 도로 경사 프리뷰 모델예측제어(MPC)로 산악 주행 에너지 8~10% 절감과 변속 충격 완화
+  - 이더넷 TSN(Time Sensitive Networking) 동기화로 제어기 간 시간 편차 100 μs 이하 확보
+  - 심층 강화학습(DRL, Deep Reinforcement Learning) 기반 변속 로직으로 변속 합리성 30%와 승차감 15% 개선
+제조·신뢰성·유지보수 통합 전략
+  - 스탬핑 마이크로채널 쿨러로 가공 비용을 CNC 대비 1/4로 절감하며 대량 생산 용이
+  - 선택적 레이저 용융(SLM, Selective Laser Melting) 일체형 스테이터로 방열 20%와 전력밀도 12~15% 향상
+  - 디지털 트윈 기반 예지정비로 고장 2~3개월 선제 예측과 비용 25~30% 및 다운타임 40% 절감</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2단 기어박스와 경량 구조 적용으로 고속 효율 5~7% 증가, 액슬 질량 15~20% 감소와 소음 8~10 dB 저감
+오일–워터 하이브리드 냉각과 고성능 TIM로 온도 변동 ±3°C 유지, 열전달 효율 25% 향상과 추가 40~50% 개선
+MPC·분산 제어·DRL로 산악 구간 소비 8~10% 감소, 토크 응답 지연 약 30% 감소, 과도 응답 30% 가속</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Frontiers in Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Electric drive axle systems in new energy vehicles</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Shandong Huayu University of Technology</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>10.3389/fmech.2026.1745639</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 1</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>전기 구동 차축 연구 지형 개요도</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 2</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>멀티스피드 기어박스·하이브리드 냉각 성능 비교</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>모터권선·3포트변압기·토템폴 기반 4-in-1 iOBC 시스템</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>EV 전력전자 4-in-1 통합으로 OBC·부스트·구동·APM 일체화와 듀얼모터 지원 구현</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>모터권선·3포트변압기·토템폴 재구성으로 PFC·APM 1차 제거와 전력단 비용 15% 절감 효과</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>차량 규격 모터와 인버터를 재활용해 AC·DC 충전, 구동, 저전압 전원을 단일 패키지로 통합
+800 V 듀얼모터 BEV에서 갈바닉 절연과 V2X를 포함한 다모드 운용을 소프트웨어로 지원</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>기존 비통합 구조는 OBC PFC·APM·인버터가 분리돼 반도체·수동소자·트랜스 수량과 비용 증가
+모터 권선 이용 iOBC는 절연 부재와 충전 토크, 인버터 스위칭 조건 불일치로 안전·효율 저하</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>모터 권선 기반 PFC·DC 부스트 충전 재구성
+  - 모터 권선을 입력 초크로 사용해 토템폴 PFC로 단상·스플릿상 충전 구현
+  - U상 직렬, V·W상 분지로 두 갈래 부스트 구성해 400→800 V DC 부스트 충전 수행
+  - 연속전도모드(CCM, Continuous Conduction Mode)로 전류 리플과 THD 저감
+3포트 변압기 기반 HV/LV 자기통합
+  - 트리플 액티브 브리지(TAB, Triple Active Bridge)와 3포트 변압기(3PT, Three-Port Transformer) 적용
+  - Port1-DC링크, Port2-HV 배터리, Port3-48 V를 결합해 갈바닉 절연 유지
+  - Port2·Port3는 듀얼 액티브 브리지(DAB, Dual Active Bridge)로 양방향 전력 흐름 구성
+인버터 토템폴 재사용과 모드 전환 로직
+  - 트랙션 인버터를 토템폴 역률보정(PFC, Power Factor Correction) 회로로 재활용
+  - SM·SP·SDC 릴레이 조합으로 구동, AC충전, DC부스트, V2X 격리·비격리 모드 선택
+  - 전력 스테이지 공유로 OBC PFC단과 APM 1차 H브리지·입력 커패시터 제거
+충전 토크 제거·동적 게이트 구동
+  - 내장형영구자석동기모터(IPMSM, Interior Permanent Magnet Synchronous Motor) q축 전류 0 규제로 토크 억제
+  - 히스테리시스 전류제어와 외부 PI 루프로 HV 배터리 전압·전류 규제
+  - 가변 게이트 저항 드라이버로 주행 10 kHz, 충전 50 kHz 조건에서 스위칭 손실 균형</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>전력단 원가 15% 절감 달성, PFC·APM 1차 제거와 3포트 자기통합으로 부품 수·트랜스 수 감소
+충전 토크 RMS 18 N·m에서 1.3 N·m로 저감, q축 전류 0 규제 제어로 주차 안전성 확보
+TAB 전력 디커플링 제어 응답 약 20 μs 달성, Port3 부하 100% 변화 시 Port2 전류 영향 최소화</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>IEEE/AIAA Transportation Electrification Conference and Electric Aircraft Technologies Symposium (ITEC+EATS)</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>SuperBox: A 4-in-1 Power Electronics Solution for Dual-Motor Electric Vehicles</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Schaeffler R</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/ITEC63604.2025.11097934</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 3</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 11</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>자기 분리 회로·다기능 브리지 일체형 온보드 차저·무선수전 토폴로지</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>온보드 차저(OBC, On-Board Charger)와 무선 전력 전송(WPT, Wireless Power Transfer)을 단일 통합 아키텍처로 구현해 EV(Electric Vehicle) 충전 비용·체적 절감</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>자기 분리 자기회로와 다기능 전력 브리지 재사용으로 모드 간 상호 간섭 차단과 고효율 ZVS 기반 구동 달성</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>OBC와 WPT를 전기적·자기적으로 분리된 단일 하드웨어로 통합
+추가 스위치 없이 안전한 모드 전환과 고효율 충전을 실현</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>모드 비분리로 OBC 동작 시 WPT 코일 전류 유발 및 EMI·과전압 위험
+기계식 스위치 의존 구조의 도통 손실 증가와 비용·신뢰성 저하</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>다기능 전력 브리지 재사용 구조
+  - HV 측 단일 액티브 브리지를 OBC와 WPT가 완전 공유하도록 구성
+  - 두 전압 배가 정류기를 병렬로 묶어 HV DC 링크 공유
+  - WPT에서는 두 하프 브리지를 능동 정류기로 재사용
+자기 분리 회로와 변압기 직렬 연결
+  - 1차를 직렬, 2차를 각각 정류기에 연결한 이중 변압기 구성
+  - 2차 권선 점표시 단자에 Rx 코일 접속해 서로 반대 전압 형성
+  - WPT 시 1차 브리지 AC단 전압을 거의 0으로 만들어 충전 차단
+모드별 스위칭 제어 및 EMI 억제
+  - OBC는 PFM(Pulse-Frequency Modulation)과 위상천이 제어 병행
+  - S5·S7 동상, S6·S8 보상 구동으로 Rx 단자 전압 동일화
+  - OBC 200kHz, WPT 85kHz로 임피던스 분리해 Rx 유도전류 최소화
+파라미터 및 공진 네트워크 설계
+  - DBSRC(Series-Resonant Dual-Active Bridge) 공진 100kHz, 스위칭 150~250kHz 설정
+  - LCC-S(Inductor-Capacitor-Capacitor-Series) 보상 설계와 L1 튜닝으로 영전압 스위칭(ZVS, Zero-Voltage Switching) 달성
+  - 전압 배가 커패시터를 DC 링크·직류차단 겸용으로 설계해 용량 확대</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1.5kW에서 OBC 피크 효율 97%, WPT 피크 효율 92% 달성
+OBC 모드 Rx 코일 단간 전압 거의 0V, WPT 시 OBC 1차 커패시터 전압 1V 이하로 디커플링 검증
+HV 측 단일 액티브 브리지 채택으로 부품 수 감소에 따른 체적·비용 저감 및 손실 경로 축소</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>2025 IEEE Wireless Power Technology Conference and Expo (WPTCE)</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>An on Board Charger and Wireless Receiver Integrated Topology Based on Decoupled Magnetic Circuit and Multifunction Power Bridge</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai Jiao Tong University</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/WPTCE62521.2025.11062164</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig.1</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>기존 WPT·OBC 통합과 탈결합 자기회로·다기능 브리지 기반 제안 통합 토폴로지 블록도</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig.5</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>OBC 및 WPT 동작 모드 핵심 파형</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>입력전류 기반 SRM IOBC 전압센서리스 충전 제어 기술</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>SRM(switched reluctance motor) 기반 IOBC(integrated on-board charging)에서 단상·3상 AC 충전의 그리드 전압 센서 제거와 비용·신뢰성 동시 달성</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>입력전류 위상동기와 OCC(one-cycle control)·AHB PWM 결합으로 전압 무검출 PFC 구현, 센서 수 1/3 감소와 THD·PF 성능 향상</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>단상·3상 충전에서 그리드 전압 센서 없이 위상 추정과 PFC를 동시 달성하는 실시간 제어 구현
+SRM 구동용 AHB(asymmetric half-bridge)와 권선을 재사용해 하드웨어 추가 없이 비용·복잡도 저감</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3상 호환 SRM IOBC는 전압·전류 센서가 다수 필요해 비용 증가와 신뢰성 저하 발생
+단상 PFC의 이중루프 PI(Proportional-Integral) 제어는 센서리스 운전에 필요한 동특성과 왜곡 내성이 부족</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>IOBC 하드웨어 재구성 및 모드 전환
+  - SRM 구동 AHB와 권선을 재사용하고 인덕터·릴레이 소수 추가로 충전 회로 구성
+  - 단상은 권선·외부 인덕터 2분기 인터리브드 부스트 PFC로 구성, 반주기 교번 스위칭
+  - 3상은 릴레이 개방으로 AHB PWM 정류기 구성, DC는 인터리브드 부스트 DC/DC로 동작
+단상 OCC 기반 전압센서리스 PFC
+  - 전압 외루프 PI 출력과 입력전류 크기를 이용해 듀티를 직접 산출하는 OCC 적용
+  - 입력전류에서 q축 성분을 추출해 위상 동기, 반주기 극성 판단으로 인터리빙 게이트 결정
+  - 전압 센서 없이도 전류-전압 동상을 유지해 고역률과 저왜형을 확보
+SOGI-SRF-PLL 기반 직교 생성과 위상 동기
+  - SOGI(second-order generalized integrator)로 입력전류의 직교 성분을 생성
+  - SRF-PLL(phase-locked loop)의 q축 제어를 0으로 유지해 위상·주파수를 추정
+  - 주파수·위상 급변 시 높은 이득으로 신속 동기 후 정상 이득으로 전환
+3상 AHB PWM 전압센서리스 PFC 제어
+  - 동기 주파수 제어기로 그리드 위상을 직접 잠금해 VOC(voltage-oriented control) 센서 의존 제거
+  - dq 전류 루프에 PI와 교차결합 보상을 적용해 모델 불확실성에 둔감
+  - 인러시 억제를 위해 전압 참조 램프와 PLL 게인 스케줄을 조합</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>전압 센서 4개→1개로 축소, 전체 센서 수 약 33% 감소로 하드웨어 복잡도와 센서 고장 위험 저감
+단상 입력전류 THD 38.42%→6.78%, PF 0.989→0.997, 출력 전압 리플 4.9%→3.5%로 저감
+위상·주파수 급변 시 약 40 ms 또는 1~2 주기 내 재동기, 부하 변동 시 20 ms 이하, 15% 전압 강하·왜곡·비대칭에서도 정상 동작</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Journal of Emerging and Selected Topics in Power Electronics</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Grid-Voltage-Sensorless Control of Integrated On-Board Charging System Based on Switched Reluctance Motors</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Nanjing University of Aeronautics</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/JESTPE.2025.3572442</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 1</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 14</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3상 구동권선 통합 충전기 자속손실 억제 인터리빙 방법</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>구동 모터·인버터를 활용한 통합 충전기에서 영구자석 동기 모터(PMSM, Permanent Magnet Synchronous Motor) 자석 가열 요인을 줄여 고출력 DC 충전을 안정화</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>대칭 대신 위상 배치(0°,180°,180°)와 스위칭 상태 선택으로 d축 전압을 0으로 만들어 자석 와전류 손실과 d축 전류 리플을 억제, 실험·FEA로 효과 검증</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>800 V 배터리 고출력 충전 시 충전 전류 리플과 로터 자석 손실을 낮춰 온도 제한 없는 지속 충전 구현
+모터 3상 권선을 모두 활용하는 통합 충전에서 추가 하드웨어 없이 제어 로직만으로 손실 억제 기술 구현</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>대칭 인터리빙은 dq 좌표(dq, direct–quadrature) d축 리플과 자속 방향 교번으로 로터 자석 와전류 손실 급증
+2상만 도통하는 방식은 상별 RMS 전류가 증가해 권선 발열과 출력 지속 시간 저하 유발</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>대칭 인터리빙에 따른 손실 메커니즘 분석
+  - 대칭 위상천이 인터리빙(interleaving)은 기본 리플 최소화 목적
+  - 그러나 d축 전류 리플이 증가해 로터 자석의 와전류 손실을 유발
+  - 자속 방향이 주기적으로 교번되어 자속이 자석에 수직 유입되는 구간이 반복
+d축 전압 0 유지를 위한 스위칭 상태 설계
+  - 로터 전기각 90°에서 스위칭 상태 S1과 S4를 교번해 d축 전압을 0으로 유지
+  - 3상 위상 배치(Φu,Φv,Φw)=(0°,180°,180°)로 두 상 상부 스위치를 교대 구동
+  - 전기각 30°·150°에서도 S3·S6 또는 S2·S5 선택으로 동일 조건 성립
+로터 각도 기반 인터리빙 위상·상태 전이 로직
+  - 전기각 60° 주기마다 유효 상태 쌍을 선택해 d축 리플 제로 조건을 유지
+  - 10 kHz PWM에서 상태 전이 시점을 균등 분할해 기본 리플 성분 억제
+  - 3상 모두 통전해 2상 통전 대비 상별 RMS 전류 상승을 방지
+제어 구현 및 검증 절차
+  - UVW 전류 센서 기반 전류 밸런스 피드백으로 상전류 불균형 보정
+  - Nissan LEAF 모터와 Si IGBT 인버터로 5~80 kW 계단 부하 실험 수행
+  - 유한요소해석(FEA, Finite Element Analysis)로 손실 분해 및 분포 검증</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>자석 손실을 전기각 90°에서 거의 0 W로 억제, 기존 최소치 약 400 W 대비 대폭 저감
+로터 자석 온도 상승 50% 감소를 실험으로 확인
+d축 전류 리플 50% 감소로 자석 와전류 손실 유발 요인 제거</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Applied Power Electronics Conference and Exposition (APEC)</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>A Novel Interleaving Method for High Power Integrated Electric Vehicle Charger with Three-Phase Permanent Magnet Synchronous Motor</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Ltd.</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/APEC48143.2025.10977458</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 1</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>제안된 인터리빙의 스위칭 상태와 dq축 전류</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 10</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>기존·제안 인터리빙의 철손 분해도</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>통합 OBC·APM용 SHB-FB 전구간 ZVS 하이브리드 변조 방법</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>650 V GaN HEMT로 700 V 버스 기반 3포트 통합 충전기 구현과 전구간 고효율 달성</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>SHB-FB의 ZVS 경계 수학모델과 DPS·TPS 결합 하이브리드 변조로 중경부하 손실 저감과 전범위 ZVS·QZVS 확보</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>OBC·APM 통합 구조에서 3상 입력과 광범위 배터리 전압을 수용하며 소자·자기부품을 공용화
+SHB-FB 단계의 전구간 ZVS·QZVS 달성을 통해 경부하시 효율과 GaN 신뢰성을 동시에 확보</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>전통 2레벨 FB DAB의 SPS 제어는 중경부하에서 ZVS 상실로 손실 증가 및 경부하 효율 저하
+3상 OBC의 높은 DC 링크에서 650 V GaN HEMT 적용이 곤란하고, 기존 DPS·TPS는 2레벨에 한정된 국부 범위 ZVS</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>통합 3포트 토폴로지와 GaN 친화 SHB 구조
+  - 1차측 SHB와 HV측 VF-FB, LV측 CF-FB를 3권선 변압기에 결합해 회로·자기 통합 구현
+  - SHB로 700 V 버스를 650 V GaN HEMT 4개로 처리하며 FB 수준의 위상 제어 자유도 확보
+  - CF-FB로 LV 대전류와 큰 권수비를 완화해 변압기 권선비와 전류 정격 저감
+SHB-FB ZVS 경계 모델링과 전류 극성 규칙
+  - Coss와 누설 인덕턴스를 기반으로 ZVS에 필요한 최소 스위칭 전류 크기 개념화
+  - 각 스위치의 ZVS 달성에 필요한 누설 전류 극성과 구간별 전류 파형 조건 정의
+  - Pri 전압과 반사 전압의 크기 관계에 따라 φ로 구간을 나누는 상태도 설계
+SPS·DPS·TPS 결합 하이브리드 변조 로직
+  - VP&gt;V'H는 1차 DPS, VP&lt;V'H는 2차 DPS를 적용하고 경부하는 TPS로 전환
+  - 외부 PS φ는 PI로 생성하고 내부 PS α, β는 경계 모델로 계산해 ZVS 유지
+  - φ 기반 상태기계로 인접 상태만 전이시켜 파형 급변을 방지
+APM 모드용 CF-DAB 듀티·위상 결합 제어
+  - HV·LV측 듀티 결합과 측간 위상으로 전력과 스위칭 전류를 분리 제어
+  - Mode1에서 전력은 위상으로, 각 포트 스위칭 전류는 해당 듀티로 독립 최적화
+  - 광범위 전압에서 모든 스위치의 ZVS 달성을 지원</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>경부하에서 SPS 대비 SHB-FB 변환기 효율이 10% 이상 향상, ZVS·QZVS 유지로 스위칭 손실과 하드턴온 제거
+OBC·V2L 피크 효율 각각 96.9%, 96.6%, 11 kW에서 95% 이상 유지
+3권선 변압기 기반 자기 통합으로 변압기 체적 54% 감소</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Transportation Electrification</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid Modulation for an SHB-FB Converter Employed in an Integrated Onboard Charger and Auxiliary Power Module</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>University of Tennessee</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TTE.2025.3562613</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 3</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>제안된 통합 온보드 충전 시스템 구조</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 18</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>SPS와 제안 HM 적용 SHB–FB 컨버터 효율 비교</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>CM 전류 공진 모델링·정량 억제 설계 방법</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>올인원 모터 구동 모듈의 공통모드(CM, Common-Mode) 전류 공진으로 저하된 전자기적 양립성(EMC, Electromagnetic Compatibility) 문제 규명과 억제 설계 정립</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>전류 진동 주파수 기반 버스바 기생 추출과 PEEC-GA로 MPBC 고주파 모델을 구축하고, 민감도 분석과 전자기 간섭(EMI, Electromagnetic Interference) Y 커패시터 정량 설계로 공진 억제 달성</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>150 kHz~30 MHz 대역에서 올인원 모듈의 CM 전류 공진 원인 규명과 지배 경로 식별
+추가 하드웨어 최소화로 규격 적합을 만족하는 EMI 정량 설계 절차 구현</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>시간영역·전압진동 방식은 절차가 번거롭고 고주파 기생의 영향 반영이 미흡
+다포트 버스 커패시터(MPBC, Multiport Bus Capacitor)의 포트 임피던스 비대칭과 내장 커패시터 추출 부재</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>전류 진동 주파수 기반 DC 버스바 기생 인덕턴스 추출
+  - 스텝 구동으로 공진 전류 스펙트럼을 계측해 공진 주파수로 버스바 인덕턴스 산출
+  - DC 커패시터·공심 인덕터를 고주파 RLC로 모델링하고 등가 직렬 인덕턴스(ESL, Equivalent Series Inductance)와 접합 커패시턴스를 포함
+  - 두 계측 지점의 공진 주파수 일치 확인으로 간섭 배제 및 추정 오차 2.8% 검증
+PEEC-GA 기반 MPBC 고주파 등가 모델링
+  - PEEC(Partial Element Equivalent Circuit)로 내부 버스바를 분할해 각 구간 기생 인덕턴스·커패시턴스 추출
+  - GA(Genetic Algorithm)로 입력·출력 임피던스 실측을 적합해 내장 커패시터의 고주파 RLC 매개변수 식별
+  - 다포트 임피던스 비대칭을 반영한 핀별 RL 모델과 버스 구간 네트워크로 전체 MPBC 모델 구성
+전체 EMI 결합 모델 구축 및 시뮬레이션 검증
+  - LISN(Line Impedance Stabilization Network)·DC 케이블·EMI(Electromagnetic Interference) 필터·모터를 CM와 DM 분해 모델로 결합
+  - IGBT 모듈 접지 커패시턴스와 버스바 기생을 포함해 CM 전류 주파수 응답을 해석
+  - 실측 스펙트럼과 비교해 16 MHz·28 MHz 공진 재현으로 모델 정확도 검증
+CM 공진 경로 민감도 분석과 Y 커패시터 정량 설계
+  - 민감도 분석으로 10~30 MHz에서 주 공진 루프를 추출하고 등가 CM 회로로 단순화
+  - 삽입 손실 목표와 누설 전류 한계를 제약으로 Y 커패시터 용량을 산정
+  - 고유 ESL을 고려해 배치 지점을 고속 충전 케이블과 MPBC 접점으로 선정</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>버스바 기생 인덕턴스 23.46 nH 추출, 임피던스 애널라이저 대비 상대 오차 2.8% 달성
+16 MHz·28 MHz 공진 경로 규명과 Y 커패시터 설계로 삽입 손실 20 dB 이상 확보
+Y 커패시터 4.7 nF 두 개 적용으로 누설 전류 제약 90 nF 이하 충족 및 CISPR 25 전도·복사 규격 만족</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Electromagnetic Compatibility</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Modeling and Suppression of Common-Mode Current Resonance in an All-in-One Motor Drive Module of Electric Vehicle</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Zhejiang University</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TEMC.2024.3503070</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 7</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>올인원 모터 구동 모듈의 전체 EMI 결합 모델</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 16</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>복사 EMI 시험 배치 구성도</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>차동모드 인덕턴스 활용 두상 모터일체형 충전 방법</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>800 V 배터리를 400 V급 기존 DC 충전기와 호환하며 효율 향상과 영토크 확보를 동시에 지향하는 모터일체형 충전 제어 기술</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>두상 180° 인터리브드와 차동모드 인덕턴스 활용으로 전류 리플·AC 손실을 억제하고, 위치 제어로 회전 억제와 95.9% 효율 및 +1.7%p 개선 달성</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>이중승압 조건에서 효율 높은 모터일체형 충전기(Integrated Charger) 제어를 구현
+충전 중 로터 정지 유지와 손실 저감을 동시 달성하는 실차 적용 가능 제어 구조 확립</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>종래 3상 부스트는 영서열 인덕턴스(Zero-Sequence Inductance) 의존으로 전류 리플과 코어·AC 도통 손실이 크게 증가
+위상 전류 DC값 동일 제약만으로 영토크를 가정해 위치 안정성 제어가 부재하며, 조건에 따라 비의도 회전 위험 존재</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>통합 충전기 인덕턴스 분해와 리플 지배 메커니즘
+  - IPMSM(Interior Permanent Magnet Synchronous Motor) 모델을 dq·영서열로 분해해 유효 인덕턴스 계산
+  - 영서열 전압(ZSV) 구동 시 유효 인덕턴스가 Lls+Lns로 작아 전류 리플이 지배됨
+  - 차동모드 전압 적용 시 Ld·Lq가 유효해 동일 전압 대비 전류 변화율이 감소
+두상 180° 인터리브드 SC2 스위칭 설계
+  - 두 상에 크기 동일·부호 반대의 전압을 인가해 영서열 전압을 상쇄
+  - 이중승압 조건에서 Gv 약 2, dH 약 0.5일 때 SC2가 ZSV를 최소화
+  - 스위칭 위상차와 주파수 설계로 전류 리플 Di와 Prem 저감을 실험 검증
+영토크 조건 해석과 TPZTC 전류 기준 생성
+  - 토크는 dq 전류와 영서열 전류의 결합으로 결정되며 영토크 조건을 곡선으로 표현
+  - 두상만 사용 시 가능한 전류 조합이 ab 평면에서 삼각형으로 제한됨
+  - 삼각형과 영토크 곡선의 교점을 따라 전류 기준을 생성해 회전 억제
+위치 제어 기반 영토크 보장 및 방법 선택 로직
+  - 전류 벡터 각도 hi를 제어량으로 사용해 토크 부호를 실시간 조절
+  - TPZTC LUT 없이도 위치 제어로 초기 각도를 유지해 다중 브레이크 역할 수행
+  - 효율 표 기반으로 SC2와 SC3를 조건부 선택해 충전 시간 최소화</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>fsw 10 kHz에서 효율 95.9% 달성, SC3 대비 +1.7%p 향상
+Ich 0~15 A 변화에서도 로터 변위 &lt;0.008 rad 유지로 영토크 실현
+Vbat 400 V 이중승압 조건에서 Prem 저감이 PdcR 증가를 상회해 총 손실 감소</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Industrial Electronics</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Two-Phase DC Charging Method for Improved Efficiency and Zero Torque in Motor-Integrated Charger</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Seoul National University</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TIE.2024.3468730</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 1</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>모터 권선·전압원 인버터 기반 통합 DC 충전 시스템 개략도</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 14</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>hr=0에서 fsw 변화에 따른 두 충전법 효율·Di 측정 결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>HEFS 모터 IOBC 구동·충전 겸용 권선 최적화 방법</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>구동·충전 겸용 통합 온보드 충전기(IOBC, Integrated On-Board Charger)에서 HEFS 하이브리드 여자 플럭스 스위칭 모터 권선 파라미터 종합 최적화</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>단일턴 상수·제약 기반 권선 수 탐색과 손실 포함 성능 평가로 5 kW급에서 출력 5.04 kW, 효율 94%대 달성</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>구동 모드 전자기 성능을 유지하며 충전 모드 출력과 효율을 극대화하는 권선 설계 확보
+추가 인덕터 없이 고조파·리플을 충족하는 IOBC용 전·계자 권선 파라미터 산출</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>기존 구동 모터를 IOBC에 적용 시 권선 파라미터 불일치로 충전 전력 저하·전류 리플 과다·효율 저하 발생
+구동·충전 이중 모드 제약을 동시 반영하는 체계적 권선 설계 절차 및 정량 지표 부재</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>HEFS 기반 IOBC 권선 설계 변수·제약 정식화
+  - 단일턴 역기전력(back-EMF)·단일턴 인덕턴스와 슬롯 전자회전수(FA) 추출
+  - 인버터 전압 한계와 역기전력 매칭, 변조지수 제약 정의
+  - AC측 리플·동특성, DC측 리플 제약으로 전·계자 권선 수 상하한 산출
+다중 운전 모드 제약 기반 권선 수 탐색
+  - 그리드 전압, DC버스, 배터리 전압, 스위칭 주기, 리플 요인 입력
+  - 전·계자 권선 조합 전수 탐색으로 충전 전력·리플·동특성 충족 여부 판정
+  - PFC(파워 팩터 코렉션, Power Factor Correction) 가능 영역과 전류 밸런싱 제어 안정 영역 동시 확인
+효율·출력 동시 평가 및 선별 로직
+  - 입력·출력전력과 동손·철손·스위칭 손실 모델로 총손실 산정
+  - 전·계자 중 출력 병목 축을 판별해 효율 계산 경로 분기
+  - 단상·삼상 충전 모두 5.04 kW 충족하는 권선 수 40/40턴 선정
+시뮬레이션·시제품 검증 및 파라미터 보정
+  - JMAG 2D FEA(유한요소해석, Finite Element Analysis)로 위상별 인덕턴스 파형 검증
+  - MATLAB/Simulink 모사로 PFC 동작·전류 밸런싱·전압 추종 검증
+  - 5 kW 시제품에 0.8 mm×5 병렬 권선 적용, 충전 효율·전력 실험 검증</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>단상 충전 효율: 시뮬레이션 94.02%, 실험 92.37%, 최적화 전 대비 각각 58.8%, 59.07% 향상
+삼상 충전 효율: 시뮬레이션 94.58%, 실험 93.00%, 최적화 전 대비 각각 51.8%, 55.08% 향상
+출력 전력 5.04 kW 달성, AC측 10%·DC측 5% 전류 리플 제약 충족 및 역률 제어 안정성 확보</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>World Electr. Veh. J.</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>An Approach to Motor Winding Optimization for HEFS Machine-Based Integrated On-Board Charging Systems</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Nanjing University of Science</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>10.3390/wevj15110502</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 1</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>통합 온보드 충전기 시스템</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 10</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>최적화된 충전 모드의 시뮬레이션 결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>뉴트럴 탭 활용 비대칭 하프브리지 스위치드 릴럭턴스 모터 삼상 통합 충전 시스템</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>SRM(Switched Reluctance Motor) 권선과 AHB(Asymmetric Half Bridge) 구동을 재사용해 IOBC(Integrated On-Board Charger)로 삼상 PFC(Power Factor Correction) 충전과 무토크 주차 구현 목적</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>하이브리드 정적·동적 피드포워드 디커플링과 준공진(quasi-resonant) 제어로 유도성 비대칭 기인 삼상 전류 불평형 90% 저감 및 DC 전압 이중주파 리플 억제</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>추가 스위치·릴레이·인덕터 없이 뉴트럴 탭만으로 삼상 PFC 충전 IOBC를 구현
+유도성 비대칭 하에서 평균 토크 0점 주차와 전류 평형을 동시에 달성</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>기존 AHB 기반 SRM IOBC는 단상 충전에 머물거나, 삼상 구현 시 다수의 추가 소자와 복잡한 제어가 필요
+SRM 권선을 필터 인덕터로 직접 재사용 시 삼상 인덕턴스 비대칭으로 전류 불평형과 DC 링크 이중주파 리플 발생</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>AHB 기반 삼상 듀얼-부스트 IOBC 토폴로지
+  - 모터 뉴트럴 포인트를 삼상 그리드에 접속해 권선을 입력 필터 인덕터로 재활용
+  - 기존 AHB 구동 스위치와 권선만으로 삼상 듀얼-부스트 PFC 정류 구성
+  - 상하암 단락 위험 제거 및 데드타임 유발 저차 고조파 억제로 THD(Total Harmonic Distortion) 저감
+무평균 토크 보장 로터 위치 선정
+  - SVPWM(Space Vector Pulse Width Modulation) 전류 파형 기반 합성 토크 모델 수립
+  - 두 상 인덕턴스 기울기 반대·한 상 영기울기 조건에서 평균 토크 0점 도출
+  - 포화 포함 유도성 비대칭 정량화로 최대·최소 인덕턴스 위치 선택 규칙 제시
+하이브리드 정정·동적 피드포워드 디커플링 제어
+  - dq 좌표 모델에서 인덕턴스 불평형의 2배주파 결합 전압 교란을 해석
+  - Lm·Lcos2n·Lsin2n과 위상 φ를 이용해 정적·동적 보상 항을 생성
+  - PI(Proportional-Integral) 전류 제어와 SVPWM에 보상 항 주입해 음수수열 전류 억제
+2ω 준공진 보강 및 강건 설계
+  - 2ω 대역 준공진 보상기를 병렬 삽입해 이중주파 음수수열 성분을 능동 제거
+  - 지배극 근사로 지연을 등가화해 대역폭 선정과 위상여유 검증 절차 정립
+  - ±50% 인덕턴스 편차 보드·나이퀴스트 해석으로 안정성 및 견실도 입증</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>삼상 전류 불평형률 ε: 20.4%→1.1%로 94.6% 감소, 최대 인덕턴스 위치 10.1%→1.0%로 90% 감소
+비대칭 전원 Ua=21V, Ub=23V, Uc=26V 조건에서 ε 92.4% 추가 저감
+위상 여유 58°, L ±50%에서 45°~65° 유지와 이득 여유 무한, 시스템 효율 93% 및 역률 1에 근접</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Power Electronics</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>An Integrated On-Board Charging Solution for EVs Driven by Switched Reluctance Motors Considering Inductance Asymmetry</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Nanjing University of Aeronautics</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TPEL.2026.3653048</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 1</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>Phase-C 최대 인덕턴스에서의 충전 전압과 토크 파형</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 20</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>Phase-C 최소 인덕턴스에서의 삼상 입력전류 THD 스펙트럼</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>OW-PMSM 기반 듀얼배터리 일체형 충전 제어 기술</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>전기차 탑재 OW-PMSM(Open-End Winding Permanent Magnet Synchronous Motor) 구동계 재구성으로 고전압·저전압 배터리 동시 충전과 충전 토크 제거 구현</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>EIC(Eight-State Interleaved Control)와 비대칭 전류 분배로 q축 상쇄를 유도해 PF&gt;0.99, THD&lt;3%, 평균 76.3% 토크 리플 억제 달성</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>듀얼 배터리 동시 충전이 가능한 탑재형 IDBC(Integrated Dual-Battery Charger) 구현과 충전 중 발생하는 OW-PMSM 토크 제거
+추가 하드웨어 최소화로 소형·경량 충전 구조를 확보하고 실차 적용 가능한 제어 프레임워크 제시</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>모터 권선을 필터로 재활용하는 IBC는 충전 전류로 인한 전자기 토크·진동·소음 증가 문제
+듀얼 배터리 충전은 추가 DC-DC와 변압기 등 부품 증가로 중량·부피·효율 저하</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>OW-PMSM 기반 IDBC 토폴로지 재구성
+  - 듀얼 인버터·개방권선을 브릿지리스 PFC(Power Factor Correction)와 병렬 벅으로 재구성
+  - 분할 권선을 필터 인덕터로 다중화해 하드웨어 추가 없이 구현
+  - K1·G1·G2로 구동모드·충전모드 전환 및 단상 AC 연계
+충전 토크 모델링과 비대칭 전류 분배
+  - dq축 등가 전류와 영구자석 토크 지배 항을 도출해 토크 성분 규명
+  - 로터 위치 의존 q축 전류를 2상 권선 전류 비대칭 분배로 상쇄
+  - 특이각 전류 폭주를 제한기 적용과 로터 자화 시프트로 회피
+8상태 인터리브드 브릿지리스 PFC 제어
+  - 반주기마다 상태 I~IV를 교번해 ib1·ic1 독립 전류 제어 구현
+  - D1·D2·D3 듀티로 ig, ib1, ic1을 분리 제어하는 인터리브드 구동
+  - 상태 전이에 따른 충전·자유순환 경로 설계로 전류 기울기 제어
+실시간 동기화 및 전류 루프 설계
+  - SOGI-PLL(Second-Order General Integrator Phase-Locked Loop)로 그리드 위상 동기
+  - 메인 배터리 전압 PI로 ig_ref 생성, θ 기반 ib1_ref·ic1_ref 산출
+  - 준 PR(Proportional-Resonant) 전류 제어로 즉시 응답과 정현 추종 확보</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>그리드 PF&gt;0.99, 입력 전류 THD 2.82%(시뮬), &lt;3%(실험)로 단상 연계 품질 확보
+토크 리플 최소 50.6% 억제, 평균 76.3% 억제, 3.84 N·m→0.83 N·m, 0.66 N·m→0.08 N·m 달성
+듀얼 배터리 168 V/42 V에서 200 W/50 W 충전, 효율 약 86%, 총 손실 32 W로 실장 가능성 확인</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Power Electronics</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>The Torque Elimination Control Strategy for Integrated Dual-Battery Charger of Electric Vehicle based on Open-End Winding Permanent Magnet Synchronous Motor</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Nanjing University of Aeronautics</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TPEL.2024.3395520</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 2</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>제안된 IDBC 시스템의 개략도</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 16</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>회전자 위치에 따른 OW-PMSM 토크 리플 변화</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>IOBC용 6상 FSCW SPM·IPM 탈자·열 동시최적 설계 기술</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>통합 온보드 배터리 충전기(IOBC, Integrated Onboard Battery Charger) 운용 시 6상 분수 슬롯 집중 권선(FSCW, Fractional Slot Concentrated Winding) 영구자석 동기 전동기(PMSM, Permanent Magnet Synchronous Motor) 자석 탈자와 발열 한계 규명</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>3차원 유한요소해석(FEA, Finite Element Analysis)·열 자기 연성과 다목표 유전 알고리즘(MOGA, Multi-Objective Genetic Algorithm)으로 12슬롯/10극 표면부착형(SPM, Surface-mounted PM) 및 매입형(IPM, Interior PM) 설계와 실증 수행</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>IOBC 운용 중 무회전 조건에서 발생하는 부분 및 불가역 탈자 메커니즘을 정량화하고 안전 운전 한계를 도출
+추가 하드웨어 없이 G2V(Grid-to-Vehicle), V2G(Vehicle-to-Grid), V2H/B(Vehicle-to-Home/Building) 구현 가능한 6상 FSCW 구동 겸용 충전 모터 설계 기준 확립</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>3상 IOBC는 회전자 토크가 남아 추가 하드웨어가 필요하고, FSCW 고조파로 PM 탈자 위험과 손실 증가
+기존 열·탈자 연구는 추진 모드 중심으로 IOBC의 정지 로터, 누설 자속, 전류 분포에 의한 PM 스트레스 반영 미흡</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>6상 비대칭 권선 IOBC 구동 및 충전 토폴로지
+  - 두 개 3상 권선 위상 분리 추진 30°, 충전 150°로 평균 토크 상쇄
+  - 권선 말단 재결선과 스위치 매트릭스(S1~S5)로 모드 전환
+  - 그리드 전류를 두 권선군에 분배해 자속 상쇄와 필터 동작 달성
+MOGA 기반 다목표 전자기 설계 최적화
+  - 목표함수에 충전 시 최대 자장과 보자력 비교 항 추가로 탈자 억제
+  - 자기 등가 회로(MEC, Magnetic Equivalent Circuit)로 초기 치수 산정
+  - 자극 두께, 이빨 폭, 코어백 두께, 슬롯 개구비 등 변수와 RSM 민감도 활용
+3D FEA 연성 열 및 탈자 리스크 평가
+  - 철손, 동손, 자석손 산출 후 TENV(Totally Enclosed Non-Ventilated) 조건 자연대류 계수로 온도 계산
+  - SPM 상자면, IPM 모서리 등 취약 지점 Bmin 추출과 무릎점 비교
+  - 최대 자장 대 보자력 비율 기반 탈자 위험도 산정과 전류 상승 시나리오 검토
+예측 전류 제어 기반 G2V 및 V2G 실증
+  - 예측 전류 제어로 xy 성분 극대화, dq에서 q축 영점으로 역률 1 달성
+  - 위상 동기 루프(PLL, Phase-Locked Loop)로 αβ 동기와 제로시퀀스 억제
+  - 15 kW IPM과 40 kW 인버터, 그리드·배터리 에뮬레이터로 실험 검증</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>IPM은 140 ℃에서도 Bmin 0.6 T 초과 유지, SPM은 0.43 T로 무릎점 이하로 저하되어 IPM의 고온 내성 확인
+100 ℃에서 IPM 탈자 위험도 전 등급 50% 미만, SPM은 50 kW 80%, 115~125 kW 95% 초과로 고위험
+충전 시 그리드 전류가 상전류의 약 1.93배, 위상 전류 THD(Total Harmonic Distortion) 약 12.3%, 역률 1 유지</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>IEEE</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Demagnetization and Thermal Analysis of Six-Phase Permanent Magnet Motor-based Integrated Onboard EV Charging</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>King Abdullah University of Science</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Demagnetization and Thermal Analysis of Six-Phase Permanent Magnet Motor-based Integrated Onboard EV Charging</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 1</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>6상 IOBC 회로 개략도와 페이저 다이어그램</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 16</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>충전 시 온도·정격별 모터 탈자 위험 비교</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>OW-PMSM 재사용 듀얼배터리 QDPC 집적 충전 시스템</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>개방권선 영구자석 동기전동기(OW-PMSM, Open-Winding Permanent Magnet Synchronous Motor)와 이중 인버터를 재사용해 삼상 그리드로 듀얼배터리를 동시 충전하고 정지 토크를 확보하는 집적 충전</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>준직접 전력 제어(QDPC, Quasi Direct Power Control)와 PR 전류 내루프를 알파-베타 좌표로 적용해 PLL·dq 해리 없이 역률 0.98 이상과 동특성 토크 맥동 1.21 N·m 달성</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>삼상 그리드 직결 환경에서 듀얼배터리 동시 충전과 모터 정지 상태의 토크 제거를 달성
+부하 불균형 시에도 두 채널 충전 전력을 정합해 입력 전류 평형과 역률 1에 근접한 운전을 구현</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>듀얼배터리 잔량 차이와 파라미터 비대칭으로 채널 간 전력 불균형 및 충전 시 전자기 토크 맥동 발생
+dq 회전좌표 기반 VSR 제어는 PLL·해리 보상이 필요해 계산량 증가와 동특성 저하 문제</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>OW-PMSM 기반 집적 충전 토폴로지
+  - 이중 인버터를 전압형 정류기(VSR, Voltage Source Rectifier)로 재구성해 듀얼배터리 동시 충전
+  - 그리드를 각 상 권선의 센터 탭에 접속하고 권선을 입력 필터 인덕터로 재사용
+  - 동상 권선의 브리지 동기 제어로 동상 전류 크기 동일·위상 반대로 흡입 자속 상쇄
+좌표계 통합과 토크 생성 메커니즘 해석
+  - 그리드 좌표와 모터 좌표를 합일화해 충전 상태 전자기 토크 항을 단순화
+  - 토크에 직류·그리드 1배·2배 주파수 맥동 성분이 포함됨을 개념적으로 도출
+  - 알파-베타 정지좌표에서 두 권선 전류를 평형시키면 평균 토크 0 조건 달성
+전력 균형 기본 제어 로직
+  - 채널별 부하 추정으로 목표 전력 일치 조건을 만족하도록 DC 전압 또는 전류 지령 산출
+  - CC/CV 모드에 따라 전압·전류 외루프 기준을 전환해 과전압을 회피
+  - 외루프 PI 통합과 직접 지령 계산으로 연산량을 경감하되 전류 평형을 유지
+QDPC와 PR 전류 내루프 설계
+  - 순시 유무효 전력 지령으로 알파-베타 전류 지령을 직접 계산하고 무효 전력 0으로 설정
+  - PR 제어기로 정지좌표 교류 전류를 무정상 추종해 PLL·dq 해리를 제거
+  - 전류루프 Kp=8, Kr=3650로 대역폭 552 Hz 확보, 전압루프 Kp=0.5, Ki=24로 감쇠비 0.707 설계</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>정지 상태 충전에서 토크 맥동 피크-투-피크 1.15 N·m 이하 달성
+변부하 동특성에서 토크 맥동 1.21 N·m, 기본 제어 1.76 N·m 대비 낮고 ΔP 18.43 W로 기본 32.75 W 대비 작음
+입력 전류 역률 0.98 이상 유지, A상 THD 실험값 4.23%·3.41%·3.76% 수준</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Transactions of China Electrotechnical Society</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Quasi-Direct Power Control of Dual-Battery Electric Vehicle Integrated Charging System Based on an Open-Winding Motor</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Nanjing University of Aeronautics</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>10.19595/j.cnki.1000-6753.tces.230426</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig.1</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>OW-PMSM 기반 이중배터리 통합 충전 토폴로지</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig.16</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>가변 부하 조건의 QDPC 전략 적용 실험 결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>유도전동기 권선 재활용 단상 IBC 이중예측 MPC 제어 기술</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>모터 구동부 재활용 단상 통합 배터리 충전기(IBC, Integrated Battery Charger)에서 단위 역률과 100 Hz 리플 억제를 동시에 달성하는 제어 체계 구현</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>모델 예측 제어(MPC, Model Predictive Control)와 이중 예측으로 스위칭 주파수 최소화, 유도전동기 권선 기반 능동 전력 분리로 DC 링크 리플 저감과 무토크 충전·V2G 지원</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>단상 그리드 연계 IBC에서 정현파·동상 그리드 전류로 단위 역률을 확보하고 충전 중 모터 토크 0을 유지
+능동 전력 분리로 100 Hz DC 링크 리플 전력을 배터리로 유입되지 않게 우회하고 스위칭 손실을 저감</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>외부 그리드 인덕터 추가가 필요해 중량·비용 증가, 단상 IBC의 2배 전원주파 리플이 배터리 열화 유발
+SPWM(sinusoidal PWM) 기반 제어는 동일 전류 리플 대비 스위칭 주파수가 높아 손실이 증가</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>단상 IBC 전력경로 및 권선 재구성
+  - 유도전동기 a,b 상 권선을 병렬로 묶어 그리드 인터페이스 인덕턴스로 활용
+  - c 상 권선을 에너지 저장 인덕터로 재활용해 능동 전력 분리(APD, Active Power Decoupling) 구현
+  - VSI 3상 인버터를 전방단 AC-DC 컨버터로 운전하며 충전 중 토크 0을 보장
+능동 전력 분리(APD) 제어 로직
+  - 그리드에서 유입되는 100 Hz 리플 전력을 c 상 권선 전류로 흡수해 DC 링크 리플 전력 우회
+  - 리플 상쇄에 필요한 c 상 기준 전류의 크기와 위상을 전력 평형 개념으로 산출
+  - 인버터 C 레그만을 변조해 c 상 전류 궤환 추종을 보장하고 추가 하드웨어 무사용
+이중 예측 기반 FCS-MPC 전류 제어
+  - 유한 제어 집합(FCS, Finite Control Set)으로 모든 스위칭 상태별 전류 궤적을 예측
+  - 오차 경계 이벤트 트리거 방식으로 제어 루프를 기동해 계산 지연을 회피
+  - 다음 최적 스위칭 상태와 유지시간을 선계산해 스위칭 횟수를 최소화
+참조 생성·동기화 및 다변수 제어 분리
+  - 위상 고정 루프(PLL, Phase-Locked Loop)로 그리드 각도 동기화 및 전류 참조 생성
+  - A,B 레그로 그리드 전류를, C 레그로 c 상 디커플링 전류를 독립 제어
+  - 코스트 함수는 전류 추종 오차와 예상 유지시간을 결합해 스위칭 주파수 저감을 목표</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>DC 링크 전압 리플이 180 V 운전에서 7 V에서 4.25 V로 감소, c 상 권선 기반 능동 전력 분리의 효과 검증
+동일 5% 전류 리플 조건에서 SPWM 대비 더 낮은 스위칭 주파수 달성으로 스위칭 손실 저감
+그리드 전류 정현파·동상으로 단위 역률 유지, 충전 중 모터 토크 0 및 V2G 모드 전력 역송 가능</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Power Electronics</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>A Model Predictive Control Scheme for a Single-Phase Integrated Battery Charger With Active Power Decoupling for EV Application</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Indian Institute of Space Science</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TPEL.2024.3350991</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>단상 통합 배터리 충전기 실험 장치 사진</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>능동 전력 디커플링 적용 전후 정상상태 파형</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>TSBC·AHBC 결합 이중원 SRM 구동·충전 통합 시스템</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>전기차(EV, Electric Vehicle)용 스위치드 릴럭턴스 모터(SRM, Switched Reluctance Motor) 구동과 이중 배터리 관리를 단일 컨버터로 고집적화하는 통합 전력변환기 개발</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>삼스위치 레그 기반 전단 DC-DC 컨버터(TSBC, Three-Switch-Based Converter)와 비대칭 하프 브리지 컨버터(AHBC, Asymmetric Half Bridge Converter) 직렬 결합과 디커플링 제어로 양방향 전력 흐름과 차량 탑재 충전기(OBC, On-Board Charger) 기능 구현</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>이중 배터리 소스를 독립적으로 제어하면서 SRM 구동과 온보드 충전을 추가 소자 없이 단일 플랫폼에서 구현
+전통 SRM 제어(CCC, APC, PWM)를 유지한 채 DC 링크 안정화와 양방향 전력관리 디커플링 제어 확립</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>병렬 이중 양방향 벅부스트 DC-DC(BBDC, Bidirectional Buck/Boost DC-DC) 구조는 스위치와 구동회로가 많아 부피·비용 증가
+다포트 컨버터는 추가 소자 다수 요구 또는 SRM 권선 재배선 필요로 실차 적용성과 신뢰성 저하</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>삼스위치 레그 TSBC 토폴로지
+  - 세 스위치 중 두 개 온·한 개 오프만 허용해 부스 쇼트와 단자 전압 부유 방지
+  - 두 입력 단자(N,M)와 각 인덕터를 통해 배터리 2개를 DC 링크에 양방향 접속
+  - S2를 공유 스위치로 두고 S1, S3와 상보 구동해 두 개 동기식 BBDC 셀로 등가화
+SRM 구동 모드 전력 흐름 제어
+  - 외부 DC 링크 전압루프와 내부 인덕터 전류루프로 Ub1이 버스 전압을 규제
+  - L2 전류 기준으로 배터리2 입출력 전력을 설정하고 잔여 전력은 배터리1이 담당
+  - S2 게이트는 S1, S3 게이트의 NAND 로직으로 생성해 세 가지 스위칭 상태만 사용
+디커플링 제어 및 변조 로직
+  - 연속전류 조건에서 인덕터 평균전압 0 제약으로 듀티를 산출해 버스 전압 범위 보장
+  - 배터리 전압 대비 버스 전압 상향 관계를 유지해 구동부 AHBC에 안정 전원 공급
+  - MOSFET(Metal Oxide Semiconductor Field Effect Transistor) 동기 정류로 순환전류 손실 저감
+온보드 충전기 재구성 방법
+  - DC 링크를 DC 소스·그리드에 접속하고 AHBC 스위치를 오프로 두어 충전 경로 구성
+  - 각 배터리 전류 추종루프로 S1, S3를 제어하고 S2는 NAND 로직으로 생성
+  - 단독 또는 동시 2포트 정전류 충전(CC) 운전을 추가 전력소자 없이 수행
+AHBC 기반 SRM 구동 로직
+  - 전류초핑제어(CCC, Current Chopping Control)와 각도위치제어(APC, Angle Position Control) 직접 적용
+  - 개루프는 가속페달 전압을 PWM 듀티로 변환해 속도를 설정
+  - 폐루프는 속도 오차 PI로 듀티 생성해 기준 속도 추종</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>병렬 이중 BBDC 대비 파워 스위치 1개와 해당 게이트 구동회로 제거로 고집적화
+스위칭 손실은 동등하고 운전 영역에 따라 도통 손실이 감소하는 동작 구간 확보
+20 kHz PWM에서 DC 링크 36 V 유지와 2500 r/min 속도 추종, 2 A 정전류 단독·동시 충전 실증</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Electric Power Systems Research</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>EV switched reluctance motor drive system with two input battery sources</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Nanjing University of Information Science</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.epsr.2025.112457</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 2</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>TSBC의 등가 컨버터 구조도</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 15</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>배터리 충전 결과 측정 파형</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>모터 권선 통합 LCL IOBC용 VSC 임피던스·안정 해석 기술</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>모터 스테이터 권선을 LCL 입력 필터로 재활용한 IOBC의 VSC 입력 임피던스 특성과 제어 안정성 정량 규명</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>dq 프레임 소신호 모델·능동 감쇠·PI 제어와 GNC 적용으로 그리드 임피던스 변화 조건에서 안정 동작 검증 및 THD 1.43% 확인</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>모터 권선 제약이 포함된 통합 LCL 필터 IOBC에서 VSC 입력 임피던스 특성과 제어 안정성 영향 규명
+전류·전압 루프 설계와 보상 전략 수립을 위한 정량 설계 지침 제공</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>기존 LCL 설계는 부품을 독립 최적화해 IOBC의 모터 유도 L2 제약을 반영하지 못함
+그리드 임피던스 변화 시 전류 루프 단독 운용에서 공진 유발과 불안정 응답 위험 존재</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>dq 프레임 기반 소신호 임피던스 모델링
+  - 평균화 모델을 선형화하고 Park 변환으로 dq 프레임 전달 함수를 도출
+  - 모터 권선이 포함된 L2·Cf를 dq 어드미턴스로 등가화해 통합 LCL 구성 반영
+  - 대각 성분 지배 가정을 적용해 해석 단순화하며 직류단 모델을 연계
+능동 감쇠·전류·전압 루프 통합 제어 설계
+  - 그리드 전류 피드백 하이패스 필터 기반 능동 감쇠로 LCL 공진 억제
+  - 전류 PI와 전압 PI를 설계하고 샘플링·연산 지연을 파데 근사로 모델링
+  - 전압 루프에서 무효전류 기준을 0으로 설정해 단위 역률 달성
+입력 임피던스 산출과 안정성 분석
+  - 전류 루프 폐루프와 전압 루프 폐루프에서 입력 어드미턴스 함수를 도출
+  - 보드 선도 비교로 저주파와 중고주파 임피던스 경향과 공진 주파수 변화 평가
+  - 그리드 임피던스와의 교차 특성으로 불안정 구간과 음의 임피던스 영역 식별
+일반화 나이퀴스트 기준 기반 안정 판별·검증
+  - 입력 임피던스 대 그리드 임피던스 비로 폐루프 안정성 조건을 판별
+  - 그리드 인덕턴스 변화 시 임계점 포위 여부로 안정·불안정 경계 확인
+  - Typhoon HIL 실시간 실험으로 파형과 THD·동특성 일치 검증</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>통합 LCL은 중고주파 영역 입력 임피던스가 더 커져 스위칭 고조파 억제 향상, 공진 주파수 1.65 kHz로 저주파 이동
+전류 루프에서 게인 여유 8.11 dB, 위상 여유 48.9° 수준 확보
+정격에서 그리드 전류 THD 1.43% 달성, 부하를 40%로 저감해도 DC 링크 전압 기준 유지</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Workshop on Control and Modeling for Power Electronics (COMPEL)</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Input Impedance and Stability Analysis of VSC in Integrated On-Board Chargers for Electric Vehicles</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>The Hong Kong Polytechnic University</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/COMPEL57542.2024.10614024</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 1</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 11</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>다권선·다주파 통합 EV WCS·OBC·APM 충전 시스템</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>무선 충전 시스템(WCS, Wireless Charging System), 온보드 충전기(OBC, On-Board Charger), 보조전원 모듈(APM, Auxiliary Power Module) 기능 통합으로 EV 고전압·저전압 배터리 충전 유연성 확보</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>다권선 결합과 주파수 튜닝으로 정전압(CV, Constant-Voltage) 출력을 달성하고 모드별 보상 토폴로지와 공유 부품으로 효율과 집적도 향상</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>EV 내 WCS·OBC·APM을 단일 플랫폼으로 통합해 비용·부피·중량을 줄이고 충전 모드 선택의 자유도 확대
+다주파 운전과 공통 부품 공유로 HV·LV 배터리의 무선·유선 동시·개별 충전 기능 구현</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>WCS·OBC·APM이 분리되어 EV 측 충전 하드웨어의 비용·부피·중량이 증가
+LV 배터리는 외부로부터 직접 유선·무선 충전이 불가하여 다중 변환을 거쳐 효율 저하</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>통합 자기결합 구조와 다권선 LV 코일 설계
+  - EV 측 OBC·HV·LV 코일 적층, 지상 측 WCS 코일과 LCC 보상 인덕터를 페라이트 양면 배치해 결합·디커플링 동시 달성
+  - 코일 크기 300 x 300 mm2, EV–지상 간격 100 mm로 WCS는 루즈 커플링, EV 내부 코일은 스트롱 커플링 형성
+  - LV 코일은 4개 대칭 권선과 각 권선 3병렬 도체를 병렬 접속해 12도체 구성, 낮은 자기 인덕턴스와 대전류 허용
+모드별 보상 토폴로지와 다주파 운전
+  - WCS-HV는 LCC-S, WCS-LV는 LCC-N로 구성하여 85 kHz에서 공진 설계
+  - OBC-HV는 S-S, OBC-LV와 APM(HV→LV)은 S-N로 구성하여 각기 245 kHz, 131 kHz, 114 kHz 운전
+  - 상호 인덕턴스 모델을 T·L 변압기 등가로 변환해 누설·여자 인덕턴스와 등가 권수비를 도출
+주파수 튜닝 기반 CV 출력 제어
+  - 보상 커패시터와 누설 인덕턴스 공진점을 기준으로 스위칭 주파수를 설정해 부하 무관 전압 형성
+  - WCS는 85 kHz에서 1차 LCC 전류를 제어해 2차 정류 후 DC 정전압을 유지
+  - OBC·APM은 전력단 변조와 공진 정합으로 2차 등가 저항 변동에 둔감한 전압 전달 확보
+모드 전환 로직과 통합 제어 아키텍처
+  - HV·LV 잔여 용량, OBC 포트 연결, WCS 결합 상태를 동시 진단해 우선순위 기반 모드 선택
+  - 상태기계로 IDLE↔각 모드 전환을 2단계 시퀀스로 수행해 연속 운전 보장
+  - 공유 스위치·인덕터·커패시터·페라이트를 제어에서 재사용해 회로 재구성 지연 최소화</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>WCS-HV(모드1)와 OBC-HV(모드3) 효율 각각 95% 초과, 부하 변동 시 CV 출력 유지
+OBC-LV(모드4)와 APM(HV→LV, 모드5) 효율 각각 90% 수준 달성
+WCS-LV(모드2) 최대 효율 80% 달성, 1차 LCC 손실 지배 요인 규명</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Industrial Electronics</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Integrating WCS, OBC, and APM Systems in Electric Vehicle Charging Systems Based on Multiwinding Couplers and Multifrequency Operation</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Fuzhou University</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TIE.2025.3600542</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>Fig.1</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>모드 1의 IDLE 전이와 정상상태 실험 파형</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>Fig.25</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>모드 3 전압·전력·효율 계산·실험 결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>시간분할 기반 EV 단상 OBC HF·LF 리플 억제 구조</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>배터리 수명 저하 원인인 고주파(HF, High-Frequency)·저주파(LF, Low-Frequency) 충전 전류 리플을 단상 온보드 충전기(OBC, Onboard Charger)에서 동시 억제하는 통합 구조 제안</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>시간분할 멀티플렉싱과 능동필터(AF, Active Filter)·인터리브드 절연 컨버터 결합으로 리플 전력 디커플링과 전 구간 제로전압스위칭(ZVS, Zero Voltage Switching) 구현</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>단상 PWM 정류기 충전에서 발생하는 2배주파 리플 전력에 의한 전력 배터리 전압·전류 리플 저감
+주행 중 보조 배터리 HF 충전 전류 리플 억제와 절연·고밀도를 동시에 만족하는 컨버터 구현</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>단상 PWM 정류기는 2배주파 맥동 전력을 유발해 배터리 과열·수명 저하를 초래하며 수동 필터는 대용량·저밀도 한계
+기존 AF는 추가 스위치·소자 필요로 전력 밀도와 통합성 저하, 보조 배터리 충전기는 HF 리플과 하드스위칭 문제 존재</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>보조 배터리 HF 리플 억제 인터리브드 절연 컨버터
+  - 저전압측 2상 인터리브드 버크–부스트 파생 구조로 H브리지 정류 결합
+  - L1·L2 전류를 180° 위상차로 동작시켜 AC 성분 상쇄로 iout 리플 상쇄
+  - 위상천이 비 제어로 전력 전달 방향·크기 결정, 전 구간 ZVS 달성
+고전압측 능동필터 기반 2배주파 리플 전력 디커플링
+  - 변압기 고전압 권선(LEST)과 에너지 저장 커패시터 Cc로 AF 경로 구성
+  - 버크 구간에서 피크 셰이빙, 부스트 구간에서 밸리 필링으로 전력 평준화
+  - 릴레이로 저전압측 차단해 순환전류 경로 제거 및 추가 손실 최소화
+시간분할 멀티플렉싱 운전·제어 로직
+  - 주행 모드: PI 전압루프 출력으로 위상천이 각도 생성해 출력 제어
+  - 주차 모드: PR(Proportional-Resonant) 전압루프로 Cc 기준 파형 추종
+  - 정류기 측 PI+PR 이중루프로 동상 전류 추종과 역률 유지
+파라미터 설계와 연속도·공진 조건 확립
+  - Cc는 주행·주차 조건식 동시 만족하도록 하한 산정해 리플 한계 보장
+  - Lks와 L1·L2는 ZVS 영역과 전류 리플 제약을 동시에 만족하도록 설정
+  - LEST·Cc 공진 주파수는 스위칭 주파수의 0.1~0.2배로 설정해 공진 회피</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>주행 모드 HF 충전 전류 리플률 0.95%(48 V, 8.4 A), 0.9%(36 V, 11.2 A), 경부하 1.43%·0.7% 달성
+주차 모드 DC버스 리플전압 4%(8 V)→1%(2 V), 배터리 리플전류 200%→90%, 입력 전류 THD 2.8%→2.5%
+전 구간 ZVS로 스위칭 손실 저감 및 고주파 동작 확보, 400 W 효율 95.20% 확인</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Power Electronics</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Integrated High- and Low-Frequency Current Ripple Suppressions in a Single-Phase Onboard Charger for EVs</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Tianjin University</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TPEL.2020.3006174</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 2</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>보조·동력 배터리 통합 충전 시스템 제안 토폴로지</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 19</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>주차 충전 모드 AF 단상 PWM 정류기 실험 결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>무토크 보장 2상 인터리브드 통합 DC 충전 방법</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>저전압 급속 DC 충전기로 고전압 EV 배터리를 승압 충전하며 구동 모터 사용 중 회전자 무토크 정지 보장</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2상 전도와 180° 인터리브드 스위칭으로 영순서 전압을 억제해 전류 리플과 철손을 감소시키는 고효율 통합 충전 제어</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>산업 표준 410–500 V 급속 충전기로 800 V급 배터리 승압 충전을 실현하고 차량 구동계를 활용하는 통합 충전 제어 구현
+충전 중 영순서 토크와 전류 리플로 인한 회전 및 철손 문제를 억제하는 무토크 제어 달성</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>세 위상 평균 전류를 동일하게 하는 종래 방식은 영순서 토크가 남아 무부하 정지 보장이 간접적임
+3상 120° 인터리브드는 전압 이득 2에서 영순서 전압 제거가 불가해 리플 증가와 철손 가중</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>무토크 곡선 기반 전류 벡터 참조 생성
+  - 영(零)순서 전류(ZSC, Zero-Sequence Current)와 영순서 쇄교의 토크 기여를 포함한 무토크 조건 해석
+  - 파크 변환(Park Transformation)과 dq 평면에서의 쌍곡선 무토크 곡선 도출
+  - 충전 전류 지령 변화에 따라 교차점 궤적으로 각 상 전류 참조를 온라인 생성
+2상 전도 영역과 제어 규칙 설계
+  - 두 상만 전도하는 선형 제약을 dq 평면에 사상해 삼각형 전도 영역 정의
+  - 무토크 곡선과 전도 영역의 교차점을 선택해 순간 무토크 점으로 전류 유도
+  - 로터 위치 추정치에 대해 교차점 갱신으로 전류 벡터를 실시간 추종
+180° 인터리브드 승압 스위칭 설계
+  - 통합 충전 토폴로지를 부스트 변환기 등가로 보고 2상 180° 인터리브드 시퀀스 구성
+  - 전압 이득 2에서 영순서 전압(ZSV, Zero-Sequence Voltage) 합을 순간마다 최소화
+  - 공통모드 인덕턴스에서의 전류 변화율을 억제해 리플 전류와 철손을 감소
+SiC 인버터 실장 및 실험 검증 로직
+  - SiC MOSFET 기반 3상 인버터와 IPMSM(Interior Permanent Magnet Synchronous Motor) 플랫폼 구성
+  - 스위칭 주파수 10–30 kHz, 400 V/200 V 스케일드 셋업에서 파형과 효율 측정
+  - 회전 변위 모니터링으로 무토크 정지 확인 및 리플 저감 효과 정량 비교</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>스위칭 30 kHz 종래 효율 95.4% 대비 제안 10 kHz에서 95.9% 달성, 저주파에서도 높은 효율 확보
+전압 이득 2에서 영순서 전압 억제로 공통모드 리플 전류 감소, 철손 저감과 발열 부담 완화
+무토크 곡선 추종으로 충전 전류 0–15 A 전 구간에서 회전 억제, 정지 상태 안전성 확보</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Applied Power Electronics Conference and Exposition (APEC)</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Two-Phase Interleaved DC Charging Method of Integrated Charger for Efficiency Enhancement</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Seoul National University</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/APEC48139.2024.10509044</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 1</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>모터 권선과 전압원 인버터를 이용한 충전 시스템 개략도</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 8</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>정격 전력에서 스위칭 주파수별 기존·제안 전략 충전 효율</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>듀얼 인버터 기반 전기차 무선충전 수신기 통합 시스템</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>전기차(EV, Electric Vehicle) 무선충전에서 수신 전력전자와 구동계를 통합해 고전력·저비용 충전 구현</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>듀얼 인버터와 오픈권선(open-winding) 모터를 DC/DC로 재구성하고 고주파 전류를 파워트레인에서 격리해 효율과 제어성 확보</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>송신기 제어·통신 없이 차량 탑재 제어만으로 정전류(CC, Constant Current)/정전압(CV, Constant Voltage) 충전 달성
+별도 수신기 전력전자 없이 드라이브트레인 재사용으로 비용·중량 저감과 고전력 수용</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>기존 무선 수신기는 별도 정류기·컨버터가 필요해 비용·중량 증가와 6.6 kW 수준 저전력 한계
+트랙션 계통으로 고주파 전류 유입 시 모터 철손·표피효과 손실과 IGBT(Insulated Gate Bipolar Transistor) 스위칭 제약</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>고주파 전류 격리형 수신기 접속 토폴로지
+  - 보상형 수신 코일을 소용량 커패시터·고속 다이오드로 듀얼 인버터 DC 링크(DC-link)에 연결
+  - 다이오드 경로 선택으로 수신 역기전력이 자동 클램프되어 배터리 전압 낮은 쪽 우선 충전
+  - 고주파 전류를 코일·다이오드·커패시터 루프에만 한정해 파워트레인 유입 차단
+듀얼 인버터 기반 멀티레벨 DC/DC 구동
+  - 두 트랙션 인버터와 오픈권선 모터를 멀티페이즈 멀티레벨 DC/DC로 구성해 DC 링크 전압 생성
+  - 동일 듀티와 상간 동기화로 제로시퀀스 전류만 인가해 토크 생성 방지
+  - 상간·인버터간 인터리빙으로 등가 리플 주파수를 스위칭의 6배로 높여 필터 용량 축소
+능동/수동 모드 운전 및 전환 로직
+  - 수동 모드에서 인버터 스위칭을 정지해 손실 최소화하며 고정 전류 수신 시 최대 전력 전달
+  - 능동 모드 B에서 듀티 사이클로 DC 링크 전압을 조절해 충전 전력을 선형 제어
+  - 스탠바이·CC·CV 상태기계로 모드 전환, 수신 코일 단락으로 안전한 기동·종료 보장
+온보드 CC/CV·에너지 밸런싱 제어
+  - 차량 탑재 디지털 신호 프로세서(DSP, Digital Signal Processor)와 센서로 CC·CV 루프 구현
+  - 비례적분 제어로 평균 전류·전압을 제어하고 느린 밸런싱 루프로 두 배터리 전압 일치
+  - 송신기는 차량 검출·전원 인가·종료만 수행해 통신 없이 동작</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>수직 간격 200 mm에서 전체 충전 효율 최대 94.3% 달성
+최대 불정렬 가로 75 mm·세로 100 mm에서도 전체 효율 80% 이상 유지
+6.6 kW 충전에서 듀티 기반 선형 전력 제어와 수신 전압 절반화로 송신 코일 전류·발열 저감</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Power Electronics</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Integrated Wireless Charging Receiver for Electric Vehicles With Dual Inverter Drives</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>University of Toronto</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TPEL.2023.3320664</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 2</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>제안된 S1–S4 재사용 통합 무선 충전기</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 20</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>최대 오정렬 가정 세 모드 전체 효율·손실 분해</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>저THD·안전 대응 GaN 기반 전면부 인덕터 IOBC 기술</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>비분리형 IOBC(Integrated On-Board Charger)의 IPMSM(Interior Permanent Magnet Synchronous Motor) 저 제로순 인덕턴스 기인 THD와 접촉전류·누설전류 안전 이슈 해결 목적</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>전면부 외장 인덕터 기반 AC/DC 부스트와 후단 모터·인버터 버크, 분할 부스트 인덕터·플로팅 EMI(Electromagnetic Interference) 필터 적용으로 THD 2.9%, PF&gt;0.95, 효율 95.9%, 비용 14.8%·부피 7.7% 절감 달성</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>일본 유틸리티 규격(&lt;5%)을 충족하는 그리드 전류 THD와 배터리 리플 전류 한도 내 제어 달성
+RCD(Residual Current Device) 오동작 방지와 UL 2202 접촉전류 시험 250 mV rms 한도 충족</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>모터·인버터를 전면부 부스트에 쓰는 기존 IOBC는 IPMSM 제로순 인덕턴스 부족으로 50 kHz에서 THD 6.9~7.1% 발생
+갈바닉 절연 부재와 낮은 공통모드 임피던스로 누설전류 증가, RCD 트립 및 인체 임피던스 전압 우려</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>구성 재배치와 전력 경로
+  - 전면부: 외장 인덕터 Le와 풀브리지 AC/DC 부스트로 PFC(Power Factor Correction) 수행
+  - 후단: 트랙션 모터 권선과 인버터를 DC/DC 버크 인덕터·스위치로 활용
+  - 저 제로순 인덕턴스 모터는 버크측에 배치해 배터리 리플 영향 최소화
+그리드측 제어 및 동기화
+  - 외부 전압 PI(Proportional-Integral)와 내부 전류 PI로 전류 파형 제어, 50 kHz 제어 주기
+  - 그리드 전압 피드포워드와 부스트 인덕턴스·디지털 지연 보상 위상 보정 적용
+  - 향상형 PLL(Phase-Locked Loop)로 전압·주파수 변동 대응 동기화
+배터리측 버크 제어·충전 전략
+  - 모터 중성점 제로순 전류 피드백 기반 전류 PI로 배터리 전류 추종
+  - SOC 20~80%는 3.6 kW 상전력, dc링크 기준 전압을 배터리 전압+30 V로 가변
+  - SOC 80~100%는 전력·전류 점감으로 스위칭 손실 억제 및 충전 시간 단축
+전기안전 네트워크와 접지
+  - 입력 분할 부스트 인덕터로 50 Hz 공통모드 누설전류 저감
+  - 플로팅 필터를 내측 루프에 배치해 50 kHz 성분 우회 경로 제공
+  - 입출력 공통모드 EMI 필터(Y 커패시터)와 TT 접지(RN 10Ω, RG 100Ω) 적용</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>그리드 전류 THD: 기존 50 kHz 6.9%, 100 kHz 7.1% 대비 수정 IOBC 2.9%, PF(Power Factor) ≥0.95 충족
+누설전류 30 mA rms 미만, 인체 임피던스 전압 250 mV rms 미만으로 IEC 61851-1·UL 2202 기준 만족
+최대 효율 95.9% @3.6 kW 달성, 배터리 리플 1.1 A p-p 유지, DAB 대비 비용 14.8%·부피 7.7% 감소</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Industry Applications</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>GaN Based Modified Integrated on-Board Charger Configuration Using Minimum Additional Active and Passive Components</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Nagoya Institute of Technology</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TIA.2025.3600210</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 6</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>부유 필터·분할 부스트 인덕터 포함 수정 IOBC 구성</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 17</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>그리드 전류 THD의 실험 결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>T형 3레벨 제로·미디엄 변조·FSBB 동기 스위칭 전기차 충전 시스템</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>전기차(EV, Electric Vehicle) 고출력 무절연 충전에서 공통 모드 전압(CMV, Common Mode Voltage)과 누설 전류 저감을 통한 안전성·소형화 달성</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>T형 3레벨에서 제로·미디엄 벡터 기반 공간 벡터 변조(SVM, Space Vector Modulation)와 4스위치 벅‑부스트(FSBB, Four‑Switch Buck‑Boost) 동기 스위칭으로 CMV 상쇄 및 누설 전류 대폭 저감</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>무절연 구조에서 인체 안전 기준을 만족하도록 CMV와 접지 누설 전류를 최소화
+추가 하드웨어 없이 변조·스위칭 전략만으로 광범위 배터리 전압대 충전 제어 구현</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>선로주파 변압기·고주파 변압기는 비용·부피·손실 부담이 크며 무절연 대안은 CMV 유발로 누설 전류와 EMI 문제가 심각
+기존 SVM 기반 감쇄법은 피크·RMS만 낮추거나 필터·보조회로를 추가해 비용·복잡도·효율 저하 유발</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>공통 모드 등가모델(CEM) 도출
+  - PFC·FSBB 각 스테이지의 스위치 노드와 접지 기생용량을 포함한 CM 경로 모델화
+  - DC 링크 커패시터의 고주파 저임피던스를 반영해 CM 해석 단순화
+  - 삼상 병렬 기생을 집약한 등가 회로로 CMV‑누설 전류 상관관계 정식화
+T형 3레벨 PFC의 제로·미디엄(ZM) 벡터 변조
+  - CMV가 0인 1개 제로 벡터와 6개 미디엄 벡터만 선택해 기준 전압 합성
+  - 두 상을 반대 방향 동시 전환하여 dv/dt를 상쇄하고 CMV 순간 변화를 제거
+  - 최근접 3벡터 합성으로 듀티를 산출하며 DC 링크 활용도는 약 86.96%로 설계
+FSBB 대칭 동기 스위칭 기반 CMV 상쇄
+  - S1·S4 동시 온, S2·S3 동시 온의 대칭 구동으로 두 스위치 dv/dt를 반상향 맞춤
+  - 연속전도(CCM)와 임계전도(CrCM)에서 전환 동기화로 접지 경로 전류 상쇄
+  - 비동기 또는 불연속전도(DCM) 시 상쇄 저하를 방지하도록 듀티·타이밍 제어
+SiC 기반 프로토타입 구현 및 폐루프 제어
+  - 탄화규소(SiC, Silicon Carbide) 소자와 LCL 필터로 실장해 고속 스위칭 검증
+  - 전단 PFC는 단위 역률 제어, 후단 FSBB는 전압 지령 추종으로 양방향 운전
+  - PLECS·LTspice 시뮬레이션과 실험으로 누설 전류·CMV 스펙트럼 검증</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>접지 누설 전류 rms 107.9 mA 대비 16.9 mA로 84.33% 감소, IEC 61851‑1·UL 2202의 30 mA 기준 만족
+CMV 노이즈 스펙트럼 최대 25.2 dB 저감, 고주파 EMI 필터 요구치 완화
+입력 500~700 V 변화 시 누설 전류 18.0~21.9 mA 수준 유지, 전압 범위 변화에 대한 강건성 확보</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Industry Applications</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Electric Vehicle Charging System Utilizing a Transformerless Common Mode Voltage Suppression Technique</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TIA.2025.3590674</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 2</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>3상 PFC·4스위치 벅부스트 비절연 2단 EV 충전기 개략도</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 15</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>제안된 변조 방식과 기존 SVM의 비교</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>공유 수신·보상·정류기 기반 유무선 충전 통합 기술</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>유도결합 설계 재구성으로 OBC(Onboard Charger)와 WPT(Wireless Power Transfer) 수신부 공유를 통한 양모드 EV(Electric Vehicle) 충전 플랫폼 제안</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Rx(Receiving) 코일·보상망·정류기 공유와 LCC-S(Inductor–Capacitor–Capacitor-Series) 1차 보상으로 상호운용 확보와 전력 밀도 향상</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>온보드 유선·무선 충전을 단일 Rx 코일·보상·정류기로 통합해 비용과 중량을 줄이는 EV 충전 아키텍처 구현
+패드 오정렬 허용도와 안전성을 유지한 채 가정·공공 인프라에서 유무선 충전 상호운용 확보</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>OBC와 WPT를 별도 탑재 시 코일·보상·정류기가 중복되어 비용·중량 증가와 전력 밀도 저하
+정류기만 공유하거나 Rx 인덕터 통합 수준에 그쳐 결합도 설계와 모드 전환 최적화의 한계</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>수신부 공유 통합 토폴로지
+  - OBC 변압기 2차를 Rx 코일로 정의하고 WPT Tx와 느슨한 결합 형성
+  - Rx 코일·보상망·정류기를 OBC와 WPT가 공용하는 단일 수신단 구성
+  - 공통 공진 주파수 설계로 두 모드에서 동일 수동소자 활용
+1차측 보상 및 동작 모드 로직
+  - WPT는 LCC-S 1차 보상으로 오정렬 시 출력이 자연 감소하도록 설계
+  - OBC는 CLLC 구조로 절연·레벨 변환과 자기정합 동작을 확보
+  - 릴레이로 OBC 1차를 개방하여 WPT 구동 시 상호 영향 차단
+자기 결합기 및 LF2 설계
+  - Rx를 OBC Tx와 적층해 강결합, WPT Tx와는 약결합을 확보
+  - LF2는 쿼드폴 구조로 두 직교 방향 탈결합을 달성해 타 코일 간 간섭 최소화
+  - 페라이트를 단측 배치해 자속 경로를 형성하고 결합 계수 목표 달성
+프로토타입 구현 및 검증
+  - 코일 크기 300×300 mm, WPT Tx–Rx 간 에어갭 100 mm로 시제작
+  - RL 20~60 Ω 범위에서 두 모드 출력과 dc–dc 효율 시뮬·실험 검증
+  - 계산·시뮬레이션·계측 일치 확인으로 제안 통합 구조의 실효성 입증</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>수신 코일·보상망·정류기 공유로 시스템 볼륨·중량·부품 수 축소 및 전력 밀도 향상
+LCC-S 기반 1차 보상으로 패드 오정렬 시 출력 자연 완화, 과전류 위험 저감과 안전성 강화
+시제작 검증에서 유무선 모두 높은 dc–dc 효율과 안정 동작 확인</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Industrial Electronics</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Integration of Onboard Charger and Wireless Charging System For Electric Vehicles With Shared Coupler, Compensation, and Rectifier</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>Fuzhou University</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TIE.2022.3204857</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 2</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>제안된 OBC 및 WPT 시스템 통합 토폴로지</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 8</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>계산·시뮬·실측 WPT/OBC 출력전력·DC-DC 효율</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>AWD EV용 병렬 IBC 전류 불평형 상쇄 구성·제어 기술</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>AWD(All Wheel Drive) EV(Electric Vehicle)의 두 구동 인버터·모터를 활용해 고출력 IBC(Integrated Battery Charger)로 온보드 급속 충전을 구현</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>IBC1을 R-Y-B, IBC2를 Y-R-B로 배선해 그리드 전류 불평형을 상쇄하고, 영순분 제어로 순환전류를 억제하는 제어 구조 제시</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>AWD EV 기존 구동 하드웨어만으로 고출력 온보드 충전 기능을 실현
+스플릿 위상 IBC의 그리드 전류 불평형과 병렬 운전 시 순환전류 문제 해결</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>스플릿 위상 기반 단일 IBC는 비대칭 권선과 맥동 자속으로 그리드 3상 전류 불평형 발생
+병렬 컨버터 공용 DC 링크 구성에서 영순분 순환전류가 흐를 경로 존재</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>AWD 구동 하드웨어 재활용 병렬 IBC 구성
+  - AWD EV의 두 모터·인버터를 병렬 IBC로 재구성
+  - 스플릿 위상 권선으로 맥동 자속 형성, 즉시 토크 0 보장
+  - 각 인버터를 전단 정류기로 동작시켜 유니티 역률로 그리드 전력 인출
+불평형 상쇄를 위한 위상 시퀀스 설계
+  - IBC1은 R-Y-B, IBC2는 Y-R-B로 연결해 각 IBC의 불평형 성분을 상호 상쇄
+  - 정지 α-β와 동기 d-q 모델에서 시간변 인덕턴스·교차결합 성분 소거
+  - 대안 구성 R-B-Y/B-R-Y, Y-B-R/B-Y-R도 불평형 저감에 유효
+순환전류 억제용 영순분 제어
+  - 영순분 전류가 공통모드 전압 차와 누설 인덕턴스에 의해 결정됨을 모델화
+  - 단일 영순분 PI 제어기로 공통모드 전압을 조절해 순환전류 억제
+  - 동일 캐리어 PWM(Pulse Width Modulation) 적용으로 고주파 순환전류 경로 제거
+전류 제어·전력 분담 및 동작 모드 관리
+  - DC 링크 전압 외부 루프가 q축 전류 기준을 생성, 분담계수 klf로 분배
+  - 각 IBC의 d,q 전류 내부 루프가 실·무효 전력을 분리 제어
+  - PLL(Phase-Locked Loop)로 그리드 각도 추정, G2V·V2G 양방향 운전 지원</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>단일 IBC 대비 충전 전력 2배 달성으로 온보드 충전 시간 단축
+실험 효율 약 94% @1 kW, 시뮬레이션 효율 88.5% @10 kW
+R-Y-B/Y-R-B 구성으로 음의 상분 상쇄되어 그리드 3상 전류 균형 확보</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Transportation Electrification</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Parallel Operation of Integrated Battery Chargers for All Wheel Drive Electric Vehicles</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Indian Institute of Space Science</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TTE.2022.3215602</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 3</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>R-Y-B/Y-R-B 기반 병렬 IBC 구성도</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 10</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>300 V·1 kW 정상상태 실험 결과—제안 R-Y-B/Y-R-B 구성</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>전류 리플 유도형 양방향 단일변압기 셀 이퀄라이저 기술</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>AGV 자동 유도 차량(AGV, Automatic Guided Vehicles) 재사용 배터리 직렬 팩의 충방전 전 과정 전압 불균형 해결 목표</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>DC-DC 인덕터를 공유한 다권선 변압기와 1차 리플 유도로 추가 스위치 없이 양방향 밸런싱을 실현하고 효율 94.2%·93.6%와 0.29→0.04 V, 0.197→0.05 V 수렴 달성</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>충전 모드(CM, Charging Mode)와 방전 모드(DM, Discharge Mode) 전 과정의 셀 전압 불균형을 자동 보정
+재사용 배터리의 균일한 사용으로 AGV 시스템 수명 연장과 에너지 활용도 제고</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>독립형 이퀄라이저는 스위치·인덕터·제어기 추가로 부피·비용 증가 및 통합 제어 복잡
+기존 통합형 변압기 기반 이퀄라이저는 충전 중에만 동작해 방전 중 불균형을 해소 불가</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>단일변압기-양방향 DC-DC 통합 구조
+  - 양방향 벅·부스트 DC-DC 인덕터를 다권선 변압기 자화 인덕턴스로 겸용
+  - 스위치 2개와 2차측 다이오드만으로 충방전 겸용 밸런싱 경로 구성
+  - 버스 전압·배터리 전류는 제어로 고정, 셀 밸런싱은 수동으로 동작
+1차 리플 전류 유도형 자동 셀 밸런싱
+  - 1차 자화 전류 리플을 2차에 유도해 각 셀에 보정 전류 생성
+  - 2차 권선 턴수 동일 설계로 저전압 셀에 더 큰 평형 전류 자연 형성
+  - 추가 스위치 없이 다이오드 정류만으로 셀 간 에너지 재분배 수행
+충방전 모드별 동작 및 제어 로직
+  - 충전 모드에서 Q1 온시 에너지 축적, 오프시 바디 다이오드 경로로 탈자
+  - 방전 모드에서 Q2 펄스폭 변조(PWM, Pulse Width Modulation)로 승압 동작
+  - 오프 구간에 1차 에너지가 2차로 결합되어 자동 평형 전류 생성
+설계 파라미터 산출 및 한계 고려
+  - 턴비 N은 허용 평형 전류 한계와 최대 셀 전압 조건으로 하한을 산정
+  - 자화 인덕턴스 Lm은 연속 전류 유지와 허용 리플 기준으로 최소값 계산
+  - 셀 수 확장 시 권선·누설 인덕턴스 증가로 장거리 직렬 팩에는 부적합</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>충전 모드 효율 94.2%, 방전 모드 효율 93.6%로 DC-DC 기능 영향 최소화
+충전 63분에 전압 편차 0.29 V→0.04 V, 방전 50분에 0.197 V→0.05 V로 수렴
+스위치 2개·다이오드 4개·단일 변압기 구성으로 기존 양방향 통합 이퀄라이저 대비 구성품 수 감소</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Industrial Electronics</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>A Double-Switch Single-Transformer Integrated Equalizer for the Recycled Power Battery String of Automatic Guided Vehicles</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>Southwest Jiaotong University</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TIE.2022.3170640</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 3</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>직렬 4셀용 제안된 이퀄라이저 구조</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 17</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>충전 모드(CM) 4셀 배터리 스트링 실험 결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>모터드라이브 재구성 기반 통합 배터리 자가가열 시스템</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>추가 하드웨어 없이 저온 성능 저하와 리튬도금 위험을 해소할 IBSH(Integrated Battery Self-Heater) 구현</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>모터 인버터 재구성과 교번 듀티 제어로 전류·전압 동시 제어를 달성해 3.45 °C/min 가열과 0.201% SOC/°C를 확보</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>구동 모터·인버터를 활용한 온보드 내부 가열을 구현해 최적 주파수 대역에서 빠르고 균일한 예열 달성
+가열 전류와 전지 전압을 동시 제어해 리튬도금과 인버터 과전류를 방지하는 안전 운용 달성</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>내부 가열용 양방향 전원과 대형 수동소자가 필요해 차량 내 공간·중량·비용 제약 심각
+고주파 가열은 3~4 C 전류 요구와 열·자기 손실 증가, 열화 메커니즘 불명확으로 신뢰성 저하</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>모터·인버터 재구성 토폴로지
+  - 트랙션 인버터와 모터 권선을 재구성해 2상 인터리브드 부스트 변환기로 동작
+  - 모터 권선을 부스트 인덕터, DC 링크 커패시터를 에너지 뱅크로 활용해 교류 가열 전류 생성
+  - 릴레이 절체로 주행 모드와 가열 모드 전환, 외부 전원 없이 배터리 자체 에너지로 구동
+저차 해석 모델과 제어지향 선형화
+  - EIS(Electrochemical Impedance Spectroscopy) 기반 ECM(Equivalent Circuit Model) 단순화 적용
+  - CPE(Constant Phase Element)·SEI(Solid Electrolyte Interphase) 영향 반영해 100~1000 Hz 유효 대역 도출
+  - 소신호 섭동으로 입력·출력 디커플링한 2차 제어지향 모델 구성
+교번 듀티 단일입력 강인 제어
+  - 단일 제어변수인 교번 듀티 비율로 피크 가열전류와 전지 단자전압을 동시 조절
+  - 출력피드백 적분 슬라이딩모드 제어로 파라미터 불확실성과 온도 변화에 강건성 확보
+  - 주기별 피크 검출로 전류·전압 경계를 실시간 추적해 리튬도금 억제와 인버터 보호 병행
+토크 제거 구동 로직
+  - 가열 전류로 유발되는 PMSM(Permanent Magnet Synchronous Motor) 토크를 전류 성분 정렬로 상쇄
+  - 공간벡터 전압 패턴으로 로터를 정렬 후 가열 모드 진입해 기계 진동과 소음 최소화
+  - 캐리어 대역으로 토크 리플을 한정해 승객 쾌적성과 잠금 장치 내구성 보장</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>3.45 °C/min 가열 속도와 0.201% SOC/°C 에너지 소모 달성, 짧은 가열 시간으로 열손실 저감
+-20 °C에서 0 °C까지 348 s 예열과 평균 에너지 소모 4.02% 달성, 전압 한계 내 충방전 유지
+피크 전류 ±6 A·±9 A는 용량 저하 없음, ±12 A는 3.182→3.047 A·h로 저하되어 전류 한계 선정 기준 제시</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Journal of Emerging and Selected Topics in Power Electronics</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Modeling and Control of an Integrated Self-Heater for Automotive Batteries Based on Traction Motor Drive Reconfiguration</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Shanghai Jiao Tong University</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/JESTPE.2021.3119599</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 2</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>IBSH 강인 제어기 블록도</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 16</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>Tb=−20°C, Ddc=0.7, f=170 Hz의 IBSH 실험 파형</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>외부 인덕터 전단·모터 후단 배치 GaN IOBC 구성 기술</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>IPMSM(Interior Permanent Magnet Synchronous Motor) 저상순 인덕턴스로 인한 단상 AC 그리드 전류 고조파 왜곡률(THD, Total Harmonic Distortion) 규격 충족을 위한 전자 구동축(E-axle) 내 통합 온보드 차저(Integrated On-Board Charger, IOBC) 구조 제안</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>모터 권선을 후단 DC/DC 벅 인덕터로, 외부 인덕터를 전단 AC/DC 부스트로 재배치한 GaN(Gallium Nitride) 기반 구성과 제어로 저차 고조파를 억제해 THD 2.9% 달성</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>저인덕턴스 IPMSM 사용 환경에서 그리드 전류 THD 5% 규격을 충족하는 단상 AC 충전 IOBC 구현
+배터리 피크투피크 전류 리플을 규격 내 유지하면서 저비용·저체적 E-axle 실장 달성</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>모터·인버터를 전단 부스트에 쓰는 기존 IOBC는 IPMSM 저상순 인덕턴스로 THD 6.9~7.1% 발생
+컨트롤러·스위칭 주파수 50 kHz 한계에서 외부 인덕터 없이 규격 충족 곤란</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>전단·후단 요소 재배치 기반 IOBC 아키텍처
+  - 외부 인덕터를 전단 AC/DC 부스트에 배치해 저주파 고조파를 전류 제어로 억제
+  - 모터 권선을 후단 DC/DC 벅 인덕터로 사용해 저상순 인덕턴스의 영향 제거
+  - 양방향 전력 경로 유지로 V2G와 비상 부하 공급 기능 호환
+GaN 전력단 및 스위칭 구성
+  - GaN HEMT 병렬 적용으로 50 kHz 구동에서 손실과 발열을 억제
+  - 전단은 정전류 형상용 PFC 스위칭, 후단은 전류 모드 벅 스위칭 적용
+  - GaN 역도통 특성에 따른 영전류 구간 클램프를 고려한 게이팅 전략 적용
+제어 루프 및 기준 생성
+  - 전단 전류 내측 루프와 전압 외측 루프로 정현 입력 전류 형상화
+  - 후단 배터리 전류 레귤레이터로 리플과 과도 응답을 규격 내 유지
+  - 단일 마이컴 50 kHz 제어 제약에서 전단·후단 파라미터 독립 조정
+설계 근거와 검증 절차
+  - H-브리지 시험으로 모터 상순 인덕턴스 50 kHz에서 135 µH 측정
+  - MATLAB 해석으로 전류 파형과 THD 스펙트럼을 구성별 비교
+  - 그리드 시뮬레이터와 저항 부하로 3.6 kW 조건의 실험 검증 수행</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>그리드 전류 THD(40차 미만): 기존 6.9%@50 kHz, 7.1%@100 kHz 대비 수정 구성 2.9%@50 kHz
+배터리 피크투피크 전류 리플 1.2 A로 동일 조건에서 규격 내 유지
+3.6 kW 실험에서 수정 IOBC는 저부하를 제외한 다수 부하 구간에서 THD 5% 미만 달성</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Energy Conversion Congress and Exposition (ECCE)</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>GaN Based Modified Integrated On-Board Charger Configuration Using Minimum Additional Active and Passive Components</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Nagoya Institute of Technology</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/ECCE53617.2023.10362905</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig.6</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>제안된 수정형 IOBC 구성도</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig.13</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>그리드 전류 THD 실험 결과 그래프</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>PIC 제어 양방향 DC-DC·스마트 BMS EV 전력관리 시스템</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>EV 가속·회생 제동에서 배터리–모터 양방향 전력 제어와 상태충전(SOC, State of Charge)·상태건강(SOH, State of Health) 실시간 추적으로 안전 운용 달성</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>PIC16F72와 배터리 관리 시스템(BMS, Battery Management System) 기반 부스트/벅 로직·임계치 자동화로 45°C 팬 구동·23 V 발전기 기동을 수행하고 90–93% 효율 확보</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>양방향 DC-DC 컨버터와 임베디드 제어로 EV 가속·회생 제동 시 고효율 전력 변환과 안전 운용 구현
+쿨롱 카운팅(Coulomb counting) SOC·용량 열화 기반 SOH 추정으로 충방전 스케줄 최적화</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>단방향 충전 구조는 회생 제동 에너지 회수 불가하고 수동 제어로 과충전·과방전 위험 상존
+정교한 SOC·SOH 실시간 추정 부재로 열폭주 대응 지연 및 변환 효율 저하</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>양방향 DC-DC 토폴로지와 PWM 제어
+  - 부스트·벅 동작으로 배터리→모터(B2M)·모터→배터리(M2B) 전력 흐름 구현
+  - 전류·전압 피드백을 이용해 펄스폭변조(PWM, Pulse Width Modulation) 듀티 제어 적용
+  - 동기 스위칭과 적정 인덕터·소자 선정으로 도통·스위칭 손실 최소화
+PIC16F72 기반 실시간 에너지 관리
+  - 1 Hz 주기로 전압·전류·온도 샘플링해 상태 변화를 상시 감시
+  - 액정표시장치(LCD, Liquid Crystal Display)·릴레이·팬·발전기 인터페이스 제어
+  - 인터럽트 기반 임계치 처리와 상태 머신으로 모드 전환 안정화
+SOC·SOH 추정과 임계치 자동화 로직
+  - 전류 누적 방식의 쿨롱 카운팅으로 SOC 산출해 충방전 한계 설정
+  - 정격 대비 가용용량 비교로 SOH 계산해 가혹 사이클 억제
+  - 45°C 이상 팬 자동 구동·23 V 미만 발전기 기동·28 V 근접 시 충전 차단
+V2G 대비 아키텍처와 확장성
+  - AC-DC 전단과 양방향 DC-DC 결합으로 차량-그리드(V2G, Vehicle-to-Grid) 경로 준비
+  - 그리드 인터페이스·동기화 모듈은 미구현이나 모듈러 확장 용이
+  - 고속 데이터·통신 필요 시 마이크로컨트롤러(MCU, Microcontroller Unit) 상향 전환 가능</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>변환 효율 90–93%(실험), 94.2%(이론)로 근접 일치하며 스위칭 안정성 확인
+고전류 구간 45°C 초과 시 팬 동작으로 배터리 온도 40°C 이하 복귀
+23 V 저전압 자동 발전기 기동 및 약 28 V 도달 시 충전 자동 종료로 과충전 방지</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>International Journal of Power Electronics and Drive System (IJPEDS)</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Bidirectional power converter for electrical vehicle with battery charging and smart battery management system</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>MLR Institute of Technology</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>10.11591/ijpeds.v16.i4.pp2592-2604</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 2</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>EV 양방향 전력변환기·배터리 충전·스마트 BMS 블록도</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 6</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>배터리 방전 중 SOC·SOH 시간 변화</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>경부하·교차부하 대응 온보드차저-보조전원 제어 기술</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>EV(Electric Vehicle)용 OBC(Onboard Charger)·APM(Auxiliary Power Module) 통합 충전에서 경부하·교차부하 시 ZVS(Zero-Voltage Switching) 상실과 LV(Low Voltage) 출력 제약 문제 해결 목적</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>VF(Variable Frequency)↔FF(Fixed Frequency) 전환과 전력 히스테리시스, TSH 기반 HV(High Voltage) 전압·TPS 기반 LV 전압 분리 제어로 고효율과 무진동 전환 구현</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>경부하에서도 LV와 HV를 독립적으로 조절해 동시 충전 품질과 시스템 신뢰성 확보
+교차부하 조건에서 ZVS 상실과 과도 리플을 억제하며 제어 안정성 유지</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>VF 상승 시 DC버스 스위치 ZVS 상실과 고주파 스위칭 손실 증가로 소자 발열과 손상 위험
+버스트 모드는 두 포트 동시 전압 리플 증가·EMI·가청소음 유발로 교차부하 독립 제어 불가</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>이중 모드 제어와 임계 전력 결정
+  - VF에서 SRC(Series Resonant Converter)와 지연시간 제어로 HV 전압 제어
+  - DSP(Digital Signal Processor) DPWM으로 게이트 펄스 생성·동기화
+  - PTH는 fswmax 170 kHz에서 LV 1 kW 전달 한계와 ZVS 경계로 산정
+경부하 고정주파 제어와 포트 분리 제어
+  - fsw 40 kHz로 고정해 스위칭 손실 억제 및 소자 발열 방지
+  - HV는 두 스위치 단락시간 TSH로 전압 제어하며 SH2·SH3는 정류 동작
+  - LV는 DAB(Dual Active Bridge) 구조에서 TPS로 독립 제어
+무진동 모드 전환 전력 히스테리시스
+  - FF 모드 최대 단락시간 Tsmax를 필요값보다 약간 크게 설정
+  - 동일 출력에서 VF fsmax와 FF Tsmax 일치시켜 VF↔FF 전환 시 진동 방지
+  - 히스테리시스 대역 약 400 W 시뮬레이션, 267 W 실험 확보
+전환 시 비선형 피드포워드 보상
+  - 전환 순간 VEA(HV)에 상수 K를 곱해 목표 정상상태 근접값으로 설정
+  - K는 전환 후 정상 VEA(HV)와 임계 VEATH의 비로 산정해 룩업 적용
+  - VHV 변동 0.2 V, VLV 변동 0.45 V로 오버·언더슈트 저감</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>경부하에서 VBus 400 V, VHV 370 V, VLV 13.8 V, PLV 240 W 조건에서 효율 96.4%(PHV 2.67 kW)와 94.4%(PHV 약 550 W) 달성
+잘못된 Tsmax로 VF↔FF 진동 시 HV·LV 리플 1.4 V·0.6 V 발생을 전력 히스테리시스로 제거하고 전환을 1주기 내 완료
+전환 시 K 적용으로 VHV 오버슈트 1.3 V→0.2 V, 언더슈트 2.5 V→0.2 V, 실험 히스테리시스 대역 약 267 W 확보</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Applied Power Electronics Conference and Exposition (APEC)</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Light-Load and Cross-Load Control of Integrated OBC and APM for Electric Vehicle Applications</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Delta Electronics (Americas) Ltd.</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/APEC43580.2023.10131194</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 6</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>충전 모드에서 통합 OBC·APM 제어 블록도</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 12</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>VBUS 400V 조건의 VF→FF 전환 시 주요 실험 파형</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>분할 권선·듀얼 인버터 기반 통합 삼상 충전 시스템</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>듀얼 인버터 구동계를 활용해 추가 전력전자 없이 EV(Electric Vehicle) 통합 삼상 온보드 충전 기능 확보 목적</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>분할 권선 기계와 CM(Common-Mode) 전압 0을 보장하는 SVPWM(Space-Vector Pulse Width Modulation)으로 충전 전류 제어와 누설 전류 억제 및 무토크 운전 달성</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>추가 전력전자 없이 구동계를 활용한 비절연 통합 삼상 온보드 충전 실현
+CM(Common-Mode) 누설전류 억제와 무토크 충전 운전으로 안전 규격 충족</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>기존 통합 충전은 공통모드 전류로 누설 전류가 커 GFCI 오동작과 안전 규격 충족 실패
+단일 인버터·접점 전환 방식은 토크 발생, 접촉기 비용 증가, 제어 복잡도 증가</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>듀얼 인버터·분할 권선 기반 통합 충전 토폴로지
+  - 각 상 스테이터를 상하 반권선으로 분할하고 분할점에 삼상 그리드를 직접 접속
+  - 두 인버터를 개별 DC 링크로 구동해 기계 내부 순환 영순서 전류 경로 제거
+  - 차체 접지와 y 커패시턴스 경로를 포함한 누설 전류 경로를 회로 수준에서 고려
+일반화 Clarke 변환 기반 4 서브시스템 분해 모델
+  - 충전, 구동, 영순서, 공통모드의 4 서브시스템으로 전류·전압 동작을 개념적으로 분리
+  - 충전 공간벡터는 그리드 전류 제어에, 구동 공간벡터는 자속·토크 생성에 독립 사용
+  - 모델 상 상호 디커플링을 보장해 각 채널의 제어 목표를 충돌 없이 설정
+CM 전압 0 보장 CH-SVPWM 변조 로직
+  - 공통모드 전압이 0이 되는 스위칭 상태 집합만 사용해 누설 전류 근본 차단
+  - 대칭 페어 상태의 체류 시간을 동일 분배해 평균 구동 전압과 영순서 전압 상쇄
+  - 섹터별 상태 시퀀스와 체류 시간 해석으로 참조 충전 전압의 주기 평균 정확 합성
+CC–CV 충전 제어와 전류 제어 구조
+  - SRF(Stationary Reference Frame) 전압 추정과 RRF(Rotating Reference Frame) 전류 제어 적용
+  - BMS(Battery Management System) 지령으로 CC–CV 전환, dq 전류 중 q축 0으로 역률 1 유지
+  - 그리드 전압 피드포워드와 참조 충전 전압 생성 후 CH-SVPWM에 전달</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>그리드 CM 전류 2.0 Arms 대비 65.4 mArms로 약 30배 감소, CM 전압 0 제약과 대칭 체류 시간으로 고주파 누설 경로 억제
+표준 인체 모델 필터 출력 308 MIU 대비 12.6 MIU로 저감, 20 MIU 한계 내 동작 입증
+7.2 kW, 20 Arms, 역률 1의 CC–CV 및 G2V·V2G 운전에서 토크 0 유지와 정현파 전류 달성</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Power Electronics</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Dual-Inverter-Integrated Three-Phase EV Charger Based on Split-Phase Machine</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>University of Toronto</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TPEL.2022.3187568</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 6</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>충전 운전 시 통합 구동계 충전기 제어 아키텍처</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 16</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>제안 변조 기법의 CM 누설전류 실험 측정</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>IMD 통합 수준 지표·IMMD·WBG 기반 설계 기술</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>전기차·항공·선박 구동의 고전력밀도·소형화를 위해 통합 전동기 구동기(IMD, Integrated Motor Drive) 구조와 통합 수준 정량 평가 체계 정립</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>모듈러 IMMD, 와이드밴드 반도체(WBG, Wide Bandgap), DC 링크 축소, LCL 필터·열·EMI 동시 설계 방법을 체계화하고 정량 지표로 비교·최적화하는 설계 지침 제시</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>분리형 대비 소형·고밀도 구동을 목표로 IMD 구조·컨버터·열·EMI의 전주기 통합 설계 원리를 정리
+IMD 통합 수준을 수치로 비교 가능한 지표화 모델을 제시해 설계 의사결정 지원</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>모터·컨버터 분리 설계로 체적·중량 증가와 케이블 손실·전자기 간섭(EMI, Electromagnetic Interference) 문제가 상존
+IMD 내부 통합 시 DC 링크 커패시터 부피·높이, 열 결합, 진동·EMI 동시 제약으로 설계 난이도·비용 증가</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>IMD 통합 수준 정량 평가 모델
+  - 출력·체적·컨버터 배치·열통합·LC 최적화·와이드밴드·모듈러 등 핵심 지표 정의
+  - 각 지표를 0~1 범위로 정규화하고 용도에 맞는 가중치로 가중 합산 점수 산출
+  - 적용 분야별 가중 설정으로 설계안 벤치마킹과 목표 적합성 판단 지원
+모듈러 IMMD 구조와 권선·전력버스 설계
+  - 분기 권선과 모듈별 컨버터로 개방권선·다상 구성을 유연하게 구현
+  - DC 버스 병렬·직렬 연결을 비교해 전류·전압 분담과 능동 균압 회로 설계
+  - 게이트 인터리빙·모듈 간 캐리어 위상 이동으로 리플과 상호간섭 저감
+DC 링크 커패시터·수동소자 부피 저감 설계
+  - 금속 필름 커패시터 채택과 RMS 전류·리플 제한 기반 용량 산정 절차 적용
+  - 질화갈륨(GaN, Gallium Nitride)·탄화규소(SiC, Silicon Carbide)로 스위칭 주파수 상향해 수동소자 축소
+  - 모듈 직렬화로 모듈당 전압 요구를 분담해 커패시터 높이 제약 대응
+LCL 필터·열·EMI 동시 통합 설계
+  - LCL을 보조 권선·보조 슬롯·라미네이션 코너 인덕터 등으로 기계적 일체화
+  - 열저항 네트워크(TRN, Thermal Resistance Network)·유한요소해석(FEA, Finite Element Analysis)·전산유체역학(CFD, Computational Fluid Dynamics) 혼합 모델로 열경로 설계
+  - 접지·차폐·능·수동 필터·에폭시 포팅·배선 단축으로 EMI 전도·복사 경로 차단</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>모터·컨버터 일체화로 케이블 단축과 하우징 공용화에 따라 시스템 비용 20~40% 절감
+와이드밴드 소자 적용으로 스위칭 주파수 5배, 도통저항 약 300배 감소로 수동소자 소형화와 효율 향상
+사각 수로 수냉 채널이 원형 대비 열 교환 성능 20% 향상</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Energies</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Overview of Integrated Electric Motor Drives: Opportunities and Challenges</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>City University of Hong Kong</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>10.3390/en15218299</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 3</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>통합 모터 드라이브(IMDs) 네 가지 분류</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 5</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>광대역갭 반도체 성능 비교</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>캐리어 위상시프트 기반 듀얼 인버터 T2A 시스템</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>전기차 보조전원 모듈(APM, Auxiliary Power Module) 제거를 목표로 듀얼 인버터에서 트랙션-보조전원(T2A, Traction-to-Auxiliary) 변환을 통합 구현</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>PWM( Pulse Width Modulation) 캐리어 위상시프트와 공진 회로로 제로시퀀스 전류를 제어해 추가 스위칭 없이 LV 버스에 전력 전달, 1.2 kW 프로토타입으로 실증</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>추가 능동 스위치 없이 듀얼 인버터만으로 T2A 전력 변환을 구현해 APM 하드웨어를 대체
+주행 및 정지 상태 모두에서 구동 토크를 교란하지 않는 LV 버스 전류 제어 로직 구현</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>전용 APM은 별도 스위치·필터로 비용·중량과 스위칭 손실이 증가
+OBC( On-Board Charger) 연계형 APM은 충전 중 동시 운용 불가 및 OBC 경로 손실이 불가피</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>제로시퀀스 기반 듀얼 인버터 T2A 전력 경로
+  - 변압기 1차와 보상 커패시터를 각 배터리 음극에 접속해 공진 루프 형성
+  - 모터 3상 전류 합을 통한 제로시퀀스 경로로 변압기 1차 전류 유도
+  - 변압기 2차 정류와 선택적 CL 필터로 LV 배터리에 DC 전력 공급
+캐리어 위상시프트 기반 제어 로직
+  - 상·하 인버터 PWM 캐리어에 위상시프트 delta를 부여해 제로축 전압 성분 생성
+  - PI( Proportional-Integral)로 iLV 오차를 보상하며 |V0| 목표를 산출해 delta로 매핑
+  - 모듈레이션 지수 M 변화를 고려해 제한기와 역삼각함수로 안정적 delta 계산
+스위칭 주파수 공진 설계
+  - 보상 커패시터와 변압기 누설 인덕턴스를 스위칭 주파수에 정합해 공진 설계
+  - 공진으로 기본파만 통과시켜 고조파 전류를 억제하고 필터 소형화 유도
+  - 변압기 여자 리액턴스는 충분히 크게 설계해 공진에 영향 배제
+기생 커패시턴스 및 신뢰성 고려
+  - dc-link Y-커패시턴스와 권선-섀시 커패시턴스를 등가 모델로 반영
+  - 권선-베어링 경로 전압이 일반 3상 드라이브 대비 같거나 작아 베어링 전류 완화
+  - Y-커패시턴스로 인한 적용 가능 전압 저하를 변압기 비와 루프 임피던스로 보상</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>추가 스위칭 동작 없이 T2A 구동으로 스위칭 손실 증가 0, 주행 효율 유지
+1.2 kW 프로토타입에서 LV 12 V, 100 A 연속 동작 및 fsw 10 kHz 운전 검증
+모터 권선에 인가된 추가 rms 전류 2.84 A로 정격 200 A의 1.5% 미만</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Power Electronics</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Auxiliary Power Module Elimination in EVs Using Dual Inverter Drivetrain</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>University of Toronto</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TPEL.2022.3176240</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 4</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>T2A 동작용 구동계 추가 회로</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 17</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>i*_LV=100 A 정상상태 T2A 동작 파형</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>구동부 재사용 듀얼 인버터 통합 3상 CSC 충전 시스템</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>구동 인버터·모터·냉각을 재사용하는 전류원 컨버터(CSC, Current Source Converter) 기반 3상 통합 충전 아키텍처 확립</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>듀얼 인버터 인터리빙·CC-CV 제어·PR 전류 제어로 PF&gt;0.99, 효율 93%, IEC 61000-3-12 충족과 무토크 충전 달성</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>3상 그리드 직결 CSC로 구동부 재사용해 고속 충전과 인프라 비용 절감 달성
+듀얼 인버터·오픈권선 PMSM으로 무토크 충전과 두 ESU 동시 CC-CV 구현</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>전압원 컨버터(VSC, Voltage Source Converter) 기반 통합 충전은 권선 재구성·브레이크 필요로 복잡·비용 증가
+과거 CSC는 SCR/GTO 저속 스위칭으로 DC 링크 리플 과다로 모터 누설 인덕턴스만으로 억제 한계</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>CSC 기반 3상 AC/DC 변환과 CSVM 구동
+  - 3상 LC 필터 후단에 전류원 컨버터 구현, DC 링크는 모터 누설 인덕턴스 활용
+  - 전류 공간 벡터 변조(CSVM, Current Space Vector Modulation)로 그리드 전류 정현파 추종 및 역률 제어
+  - 스위칭 시퀀스 오버랩 시간 관리로 스위치 스트레스와 전류 연속성 확보
+듀얼 인버터·오픈권선 PMSM 기반 DC/DC 구성
+  - 듀얼 인버터가 두 에너지 저장 장치(ESU, Energy Storage Unit)를 개별 포트로 연결해 혼합 매체 수용
+  - 평균 모델 기반 PWM로 각 권선 전압·전류를 독립 제어해 충전 전류 형상화
+  - 오픈권선 PMSM(Permanent Magnet Synchronous Motor) 적용으로 충전 중 DC 균형 전류만 흐름
+인터리빙 스위칭으로 DC 링크·권선 리플 저감
+  - 인버터 간 위상천이와 권선 간 위상천이를 조합한 인터리빙 적용
+  - CSC와 듀얼 인버터 스위칭 주기 비 조정으로 리플 상쇄 조건 만족
+  - 유효 스위칭 주파수 상승 효과로 필터 소형화와 열 스트레스 저감
+그리드 전류·CC-CV·밸런싱 통합 제어
+  - 비례-공진(PR, Proportional-Resonant) 그리드 전류 내측 루프와 비례-적분(PI, Proportional-Integral) 전력 외측 루프 구성
+  - 정전류·정전압(CC-CV, Constant-Current Constant-Voltage) 중첩 제어로 2개 ESU에 독립 CC-CV 충전 수행
+  - 권선 전류 밸런스·ESU 충전 상태(SoC, State of Charge) 밸런스 PI 제어로 모터 토크 억제와 에너지 분배</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>10kW 프로토타입에서 전력인자(PF, Power Factor) &gt;0.99 달성, PR 전류 제어와 CSVM으로 그리드 전류 정현파화
+정격 전력에서 전체 효율 93% 달성, 듀얼 인버터 인터리빙으로 스위칭·전도 손실 분산
+IEC 61000-3-12 그리드 전류 고조파 한계 충족, LC 필터와 전류 제어로 규격 대응</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>University of Toronto</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>A 3-Phase Electric Vehicle Charger Integrated with Dual Inverter Drive</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>University of Toronto</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>A 3-Phase Electric Vehicle Charger Integrated with Dual Inverter Drive</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 1.6</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>AC 레벨1·레벨2/급속 통합 충전 개요도</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Figure 4.17</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>슈퍼커패시터 ESU 기반 프로토타입 구성도</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>논문</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>모터부스트·절연 OBC 통합용 4-레그 결합자기 전력 모듈</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>48 V 저전압 구동계에서 모터 부스트 구동과 절연 온보드 충전을 단일 모듈로 통합해 소형화와 고효율을 달성하는 전력 변환 통합 구조 제안</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>결합자기 소자(CMD, Coupled Magnetic Device)와 위상 제어로 인덕터·트랜스포머 동작을 전환하고 4-레그 구조로 전력 밀도 12%와 BC 효율 1.5% 향상 및 구동 효율 2.5% 개선</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>48 V 저전압 EV에서 고전류 손실·발열을 억제하면서 부스트 모터 구동과 절연 온보드 충전기(OBC, On-Board Charger)를 하나의 모듈로 구현
+모듈 수와 코어·권선 규모를 줄여 A4 사이즈 내 집적 가능한 구동·충전 통합 전력 모듈 실현</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>저전압 고출력 구동에서는 인버터(INV, Inverter)와 모터에 대전류가 흐르며 도통 손실과 냉각 복잡도, 체적이 증가
+모터 중성점 기반 절연 충전 통합 방식은 소자 수가 많고 배선·코스트 증가로 소형화에 한계</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>4-레그 결합자기 소자 구조
+  - 결합자기 소자(CMD, Coupled Magnetic Device) 4-레그 정사각 코어 채택으로 유도 인덕턴스 대폭 증대
+  - 1차 4권선(N1a~N1d) 병렬 부스트 컨버터(BC, Boost Converter)에 연결, 2차는 직렬 접속으로 동손 저감
+  - 중심 탭을 배터리에 연결해 전류 경로를 단축하고 권선 수를 최소화해 권선 손실 저감
+위상 제어 기반 이중 동작 모드
+  - 모터 구동 시 BC 팔을 동상·역상으로 배치해 인덕터 동등 형성, 전류 리플 40 App 기준 설계
+  - 온보드 충전기(OBC, On-Board Charger) 시 팔간 180° 위상차로 2차 유기 전압 생성, 절연 트랜스포머 동작
+  - 부스트비 1:2 조건에서 상호 결합과 인터리빙으로 권선 리플 상쇄해 스위칭 손실 저감
+통합 제어 및 AC 인터페이스
+  - 모드 셀렉터로 모터·충전 모드 전환, vdc와 배터리 전류를 비례적분(PI, Proportional–Integral)로 제어
+  - 단상 매트릭스 컨버터(MC, Matrix Converter)에 펄스 밀도 변조(PDM, Pulse Density Modulation) 적용
+  - 그리드 동기 전류 제어로 역률 0.99 이상과 THD 5% 미만 달성, 양방향 전력 흐름 지원
+A4 모듈 하드웨어 아키텍처
+  - BC·인버터(INV, Inverter)를 병렬 배치해 직구동 영역 도통 손실 최소화
+  - GaN-FET(Gallium Nitride Field-Effect Transistor) 보드와 8층 PCB로 고주파 저손실 스위칭 구현
+  - 4-레그 CMD 58×58 mm 코어와 1차-2차(P-S, Primary-Secondary) 교번 권선으로 집적</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>4-레그 CMD와 정사각 코어 채택으로 전력 밀도 12% 증가, 동일 리플에서 스위칭 주파수 185 kHz 달성
+3-레그 대비 BC 효율 1.5% 향상, 코어·스위칭 손실 28% 감소와 권선 손실 7% 감소로 총손실 35% 감소
+표준 비부스트 대비 5 kW에서 구동 효율 2.5% 개선, 5 kW 94.5%·AC100V 3 kW 충전 90%·PF 0.99·THD 5% 달성</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Transportation Electrification</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Coupled Magnetic-Based Integrated Isolated Onboard Battery Charger and Boost Motor Drive Unit for Electric Vehicles</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Toyota Central R</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>10.1109/TTE.2021.3093488</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 5</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>CMD 기반 BC·INV 병렬·MC(100/200V) 구성</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>Fig.Fig. 35</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>부스트 구동 3·4레그 CMD 효율 비교</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T8"/>
+  <autoFilter ref="A1:T54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>